--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.906840377746043e-14</v>
+        <v>9.940793884389218e-15</v>
       </c>
       <c r="B2" t="n">
-        <v>-87.4783287397218</v>
+        <v>65.34293325112765</v>
       </c>
       <c r="C2" t="n">
-        <v>-44.92753384873855</v>
+        <v>31.09242904364742</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.119441269042587</v>
+        <v>4.552802535897987</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2976260566656013</v>
+        <v>0.2932054216663521</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>200.978964735862</v>
+        <v>198.4616961007698</v>
       </c>
       <c r="H2" t="n">
-        <v>419.2550334185198</v>
+        <v>442.9789105217176</v>
       </c>
       <c r="I2" t="n">
-        <v>273.2128864244356</v>
+        <v>475.7156190264243</v>
       </c>
       <c r="J2" t="n">
-        <v>265.5521303757528</v>
+        <v>416.0547430373032</v>
       </c>
       <c r="K2" t="n">
-        <v>469.0595782381198</v>
+        <v>259.5881299704866</v>
       </c>
       <c r="L2" t="n">
-        <v>196.6976154812673</v>
+        <v>207.5549464928588</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.320185187957069e-14</v>
+        <v>-1.211857004082994e-14</v>
       </c>
       <c r="B3" t="n">
-        <v>-70.5520593460455</v>
+        <v>63.17971053312377</v>
       </c>
       <c r="C3" t="n">
-        <v>-31.59057597813808</v>
+        <v>29.96411308237163</v>
       </c>
       <c r="D3" t="n">
-        <v>7.48780401567207</v>
+        <v>4.011725325234443</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4314901214634457</v>
+        <v>0.2072849715388669</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>335.9021650725254</v>
+        <v>292.6916163800972</v>
       </c>
       <c r="H3" t="n">
-        <v>263.9183838665536</v>
+        <v>253.4092586536476</v>
       </c>
       <c r="I3" t="n">
-        <v>253.8460937337564</v>
+        <v>171.2688600913488</v>
       </c>
       <c r="J3" t="n">
-        <v>274.4492823069505</v>
+        <v>360.1673697718163</v>
       </c>
       <c r="K3" t="n">
-        <v>257.5730072498108</v>
+        <v>261.1959069984936</v>
       </c>
       <c r="L3" t="n">
-        <v>271.3540674232028</v>
+        <v>254.6744929531627</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8.36678832056133e-16</v>
+        <v>-1.202050186406843e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>93.44180125062124</v>
+        <v>66.02934538380599</v>
       </c>
       <c r="C4" t="n">
-        <v>47.24488245604631</v>
+        <v>31.20626981426283</v>
       </c>
       <c r="D4" t="n">
-        <v>8.083949926262365</v>
+        <v>4.627985916719141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4567861837796905</v>
+        <v>0.01038044178291492</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>452.58692417201</v>
+        <v>392.4576527544643</v>
       </c>
       <c r="H4" t="n">
-        <v>260.3265042171874</v>
+        <v>315.3133828712684</v>
       </c>
       <c r="I4" t="n">
-        <v>464.3776718085873</v>
+        <v>422.8719070916732</v>
       </c>
       <c r="J4" t="n">
-        <v>265.248107739254</v>
+        <v>229.5465237936813</v>
       </c>
       <c r="K4" t="n">
-        <v>372.303017380591</v>
+        <v>163.3831916726887</v>
       </c>
       <c r="L4" t="n">
-        <v>294.9455572659506</v>
+        <v>310.0181460888315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.563689921527257e-16</v>
+        <v>5.163206326778676e-16</v>
       </c>
       <c r="B5" t="n">
-        <v>-93.54228569982023</v>
+        <v>-65.90624776213046</v>
       </c>
       <c r="C5" t="n">
-        <v>-47.22773895539017</v>
+        <v>-31.08091462613098</v>
       </c>
       <c r="D5" t="n">
-        <v>-8.142329390856107</v>
+        <v>-4.628003896141625</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05907845362338124</v>
+        <v>0.1471823220750438</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>434.1933312009734</v>
+        <v>464.7851105829653</v>
       </c>
       <c r="H5" t="n">
-        <v>417.4151843832235</v>
+        <v>462.9870802959828</v>
       </c>
       <c r="I5" t="n">
-        <v>175.7214267727509</v>
+        <v>209.6939095995413</v>
       </c>
       <c r="J5" t="n">
-        <v>187.773893109408</v>
+        <v>261.0271580505594</v>
       </c>
       <c r="K5" t="n">
-        <v>427.4358075859643</v>
+        <v>371.8833917410598</v>
       </c>
       <c r="L5" t="n">
-        <v>471.0985910221617</v>
+        <v>334.1153275320588</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4.870322634268902e-16</v>
+        <v>-8.343678331145212e-18</v>
       </c>
       <c r="B6" t="n">
-        <v>33.33768559756777</v>
+        <v>24.34101662537363</v>
       </c>
       <c r="C6" t="n">
-        <v>47.41234586782812</v>
+        <v>31.23460795245</v>
       </c>
       <c r="D6" t="n">
-        <v>8.167392396291259</v>
+        <v>4.631316851653938</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3921182653992667</v>
+        <v>-0.1362989576572911</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>330.5299886408145</v>
+        <v>160.1374851976115</v>
       </c>
       <c r="H6" t="n">
-        <v>175.5681266982127</v>
+        <v>199.4972526483417</v>
       </c>
       <c r="I6" t="n">
-        <v>165.9719991178358</v>
+        <v>183.430394755112</v>
       </c>
       <c r="J6" t="n">
-        <v>255.3145865083272</v>
+        <v>241.711525274946</v>
       </c>
       <c r="K6" t="n">
-        <v>226.1815925256488</v>
+        <v>379.3637988858356</v>
       </c>
       <c r="L6" t="n">
-        <v>417.1513532326182</v>
+        <v>345.8556050598332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-4.886826871014718e-15</v>
+        <v>1.014688373348133e-15</v>
       </c>
       <c r="B7" t="n">
-        <v>-79.80793930816814</v>
+        <v>-30.57030797746024</v>
       </c>
       <c r="C7" t="n">
-        <v>-47.42032644821675</v>
+        <v>-31.23457131638467</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.174101035452695</v>
+        <v>-4.623845117484152</v>
       </c>
       <c r="E7" t="n">
-        <v>0.208910054340789</v>
+        <v>-0.2973545598157386</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>237.071645924889</v>
+        <v>342.7813656293661</v>
       </c>
       <c r="H7" t="n">
-        <v>390.9878775499664</v>
+        <v>183.1703678437171</v>
       </c>
       <c r="I7" t="n">
-        <v>303.575828908203</v>
+        <v>292.7876326550343</v>
       </c>
       <c r="J7" t="n">
-        <v>439.5658933273985</v>
+        <v>427.4767156303036</v>
       </c>
       <c r="K7" t="n">
-        <v>225.7310724470435</v>
+        <v>307.5621396938427</v>
       </c>
       <c r="L7" t="n">
-        <v>275.2347621265649</v>
+        <v>342.8459931841588</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.784591557188293e-17</v>
+        <v>8.229926309129317e-17</v>
       </c>
       <c r="B8" t="n">
-        <v>22.21233985291162</v>
+        <v>-27.66605975679562</v>
       </c>
       <c r="C8" t="n">
-        <v>1.271083927969595</v>
+        <v>1.067647483400888</v>
       </c>
       <c r="D8" t="n">
-        <v>8.178870824123793</v>
+        <v>4.633267345186171</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0389040799306172</v>
+        <v>-0.01674395573535175</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>238.2390507724944</v>
+        <v>244.8777788044186</v>
       </c>
       <c r="H8" t="n">
-        <v>180.9949069910149</v>
+        <v>414.586869905781</v>
       </c>
       <c r="I8" t="n">
-        <v>383.9994766329008</v>
+        <v>198.9677921464707</v>
       </c>
       <c r="J8" t="n">
-        <v>404.4665465836748</v>
+        <v>193.4914271019785</v>
       </c>
       <c r="K8" t="n">
-        <v>445.6651848360959</v>
+        <v>175.1605859195013</v>
       </c>
       <c r="L8" t="n">
-        <v>470.5215008511884</v>
+        <v>271.7000874512382</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.544729061205824e-16</v>
+        <v>6.66682269851009e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>-22.86111112737582</v>
+        <v>-42.42638830924984</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.39294574615993</v>
+        <v>-12.03506969916373</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.178960309174476</v>
+        <v>-4.633474617794199</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01320852228974013</v>
+        <v>-0.004670479181094366</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>185.720112861381</v>
+        <v>252.3577601870796</v>
       </c>
       <c r="H9" t="n">
-        <v>299.7139237501492</v>
+        <v>386.1080042037839</v>
       </c>
       <c r="I9" t="n">
-        <v>273.7469919470015</v>
+        <v>377.0751564747108</v>
       </c>
       <c r="J9" t="n">
-        <v>164.5094509118574</v>
+        <v>464.6846390562647</v>
       </c>
       <c r="K9" t="n">
-        <v>252.0111985960657</v>
+        <v>232.7650087767408</v>
       </c>
       <c r="L9" t="n">
-        <v>324.3721574624751</v>
+        <v>220.7429079866505</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.819951432443388e-16</v>
+        <v>1.289258457479122e-16</v>
       </c>
       <c r="B10" t="n">
-        <v>57.0061443777109</v>
+        <v>11.17117782101327</v>
       </c>
       <c r="C10" t="n">
-        <v>46.59199604175333</v>
+        <v>-21.98828482354696</v>
       </c>
       <c r="D10" t="n">
-        <v>8.148955586121032</v>
+        <v>4.617457403845774</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6984893357601661</v>
+        <v>0.3845803842123143</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>273.1351865204107</v>
+        <v>327.4294104484989</v>
       </c>
       <c r="H10" t="n">
-        <v>327.3967204238076</v>
+        <v>453.5492980307675</v>
       </c>
       <c r="I10" t="n">
-        <v>393.9188070174911</v>
+        <v>224.241542422005</v>
       </c>
       <c r="J10" t="n">
-        <v>350.1192212637804</v>
+        <v>224.0119019676069</v>
       </c>
       <c r="K10" t="n">
-        <v>173.3570317154415</v>
+        <v>328.0292642692195</v>
       </c>
       <c r="L10" t="n">
-        <v>175.0399004523184</v>
+        <v>317.79303542216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.479422537912927e-15</v>
+        <v>8.882522817996928e-16</v>
       </c>
       <c r="B11" t="n">
-        <v>82.18102101303</v>
+        <v>-43.51395682176951</v>
       </c>
       <c r="C11" t="n">
-        <v>42.54501108270538</v>
+        <v>-29.97595638852331</v>
       </c>
       <c r="D11" t="n">
-        <v>8.147346778232107</v>
+        <v>-4.61627346876385</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6983023895785728</v>
+        <v>-0.3844803120888034</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>212.4108710153792</v>
+        <v>431.454502347732</v>
       </c>
       <c r="H11" t="n">
-        <v>438.8450594465903</v>
+        <v>292.391012321192</v>
       </c>
       <c r="I11" t="n">
-        <v>367.7533668339651</v>
+        <v>268.4439002683727</v>
       </c>
       <c r="J11" t="n">
-        <v>290.8627023688921</v>
+        <v>425.3246468850106</v>
       </c>
       <c r="K11" t="n">
-        <v>332.9147200165917</v>
+        <v>367.9640033327566</v>
       </c>
       <c r="L11" t="n">
-        <v>303.6910501712843</v>
+        <v>198.9453684981033</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>441.3040692247347</v>
+        <v>300.1896575890655</v>
       </c>
       <c r="H12" t="n">
-        <v>467.4541804898262</v>
+        <v>460.4727091357807</v>
       </c>
       <c r="I12" t="n">
-        <v>186.8226739142778</v>
+        <v>451.4362730085228</v>
       </c>
       <c r="J12" t="n">
-        <v>242.7915029261704</v>
+        <v>175.3441372842708</v>
       </c>
       <c r="K12" t="n">
-        <v>218.9319690788675</v>
+        <v>247.3971304394904</v>
       </c>
       <c r="L12" t="n">
-        <v>208.1457134494238</v>
+        <v>446.2664022331443</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>441.3040692247347</v>
+        <v>300.1896575890655</v>
       </c>
       <c r="H13" t="n">
-        <v>467.4541804898262</v>
+        <v>460.4727091357807</v>
       </c>
       <c r="I13" t="n">
-        <v>186.8226739142778</v>
+        <v>451.4362730085228</v>
       </c>
       <c r="J13" t="n">
-        <v>242.7915029261704</v>
+        <v>175.3441372842708</v>
       </c>
       <c r="K13" t="n">
-        <v>218.9319690788675</v>
+        <v>247.3971304394904</v>
       </c>
       <c r="L13" t="n">
-        <v>208.1457134494238</v>
+        <v>446.2664022331443</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.906840377746043e-14</v>
+        <v>9.940793884389218e-15</v>
       </c>
       <c r="B15" t="n">
-        <v>93.44180125062124</v>
+        <v>66.02934538380599</v>
       </c>
       <c r="C15" t="n">
-        <v>47.41234586782812</v>
+        <v>31.23460795245</v>
       </c>
       <c r="D15" t="n">
-        <v>8.178870824123793</v>
+        <v>4.633267345186171</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6984893357601661</v>
+        <v>0.3845803842123143</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9.940793884389218e-15</v>
+        <v>4.333519793092376e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>65.34293325112765</v>
+        <v>14.32970207851291</v>
       </c>
       <c r="C2" t="n">
-        <v>31.09242904364742</v>
+        <v>3.866825595790485</v>
       </c>
       <c r="D2" t="n">
-        <v>4.552802535897987</v>
+        <v>0.1867912526209001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2932054216663521</v>
+        <v>0.0008579083623691486</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>198.4616961007698</v>
+        <v>155.239055293018</v>
       </c>
       <c r="H2" t="n">
-        <v>442.9789105217176</v>
+        <v>268.7996574166283</v>
       </c>
       <c r="I2" t="n">
-        <v>475.7156190264243</v>
+        <v>120.7042447589839</v>
       </c>
       <c r="J2" t="n">
-        <v>416.0547430373032</v>
+        <v>232.2635270345889</v>
       </c>
       <c r="K2" t="n">
-        <v>259.5881299704866</v>
+        <v>324.7167866562738</v>
       </c>
       <c r="L2" t="n">
-        <v>207.5549464928588</v>
+        <v>172.3554033854167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.211857004082994e-14</v>
+        <v>-4.626097186756907e-16</v>
       </c>
       <c r="B3" t="n">
-        <v>63.17971053312377</v>
+        <v>3.32380072754209</v>
       </c>
       <c r="C3" t="n">
-        <v>29.96411308237163</v>
+        <v>-3.612831347902668</v>
       </c>
       <c r="D3" t="n">
-        <v>4.011725325234443</v>
+        <v>0.01203443264648458</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2072849715388669</v>
+        <v>-0.0005248379813055048</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>292.6916163800972</v>
+        <v>126.298814844755</v>
       </c>
       <c r="H3" t="n">
-        <v>253.4092586536476</v>
+        <v>216.0676442175127</v>
       </c>
       <c r="I3" t="n">
-        <v>171.2688600913488</v>
+        <v>289.4538859265093</v>
       </c>
       <c r="J3" t="n">
-        <v>360.1673697718163</v>
+        <v>252.8933605583935</v>
       </c>
       <c r="K3" t="n">
-        <v>261.1959069984936</v>
+        <v>224.8385547745061</v>
       </c>
       <c r="L3" t="n">
-        <v>254.6744929531627</v>
+        <v>338.8836419862683</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.202050186406843e-16</v>
+        <v>5.831630857015175e-18</v>
       </c>
       <c r="B4" t="n">
-        <v>66.02934538380599</v>
+        <v>18.22655570992734</v>
       </c>
       <c r="C4" t="n">
-        <v>31.20626981426283</v>
+        <v>5.055743683585101</v>
       </c>
       <c r="D4" t="n">
-        <v>4.627985916719141</v>
+        <v>0.1955330917041322</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01038044178291492</v>
+        <v>-0.007530158502224977</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>392.4576527544643</v>
+        <v>219.2313331751081</v>
       </c>
       <c r="H4" t="n">
-        <v>315.3133828712684</v>
+        <v>128.9995092647846</v>
       </c>
       <c r="I4" t="n">
-        <v>422.8719070916732</v>
+        <v>354.1295950808803</v>
       </c>
       <c r="J4" t="n">
-        <v>229.5465237936813</v>
+        <v>328.1288015049099</v>
       </c>
       <c r="K4" t="n">
-        <v>163.3831916726887</v>
+        <v>299.5968285520432</v>
       </c>
       <c r="L4" t="n">
-        <v>310.0181460888315</v>
+        <v>398.84889378004</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5.163206326778676e-16</v>
+        <v>1.660676677639394e-17</v>
       </c>
       <c r="B5" t="n">
-        <v>-65.90624776213046</v>
+        <v>-9.122017648126123</v>
       </c>
       <c r="C5" t="n">
-        <v>-31.08091462613098</v>
+        <v>-5.057369306583921</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.628003896141625</v>
+        <v>-0.1961165214039462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1471823220750438</v>
+        <v>0.00712352314118656</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>464.7851105829653</v>
+        <v>94.73192944856265</v>
       </c>
       <c r="H5" t="n">
-        <v>462.9870802959828</v>
+        <v>164.9460680543654</v>
       </c>
       <c r="I5" t="n">
-        <v>209.6939095995413</v>
+        <v>276.7068012752046</v>
       </c>
       <c r="J5" t="n">
-        <v>261.0271580505594</v>
+        <v>209.4676251409578</v>
       </c>
       <c r="K5" t="n">
-        <v>371.8833917410598</v>
+        <v>251.6464575009193</v>
       </c>
       <c r="L5" t="n">
-        <v>334.1153275320588</v>
+        <v>187.6528711351712</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-8.343678331145212e-18</v>
+        <v>-6.465077602175565e-17</v>
       </c>
       <c r="B6" t="n">
-        <v>24.34101662537363</v>
+        <v>12.54266116535535</v>
       </c>
       <c r="C6" t="n">
-        <v>31.23460795245</v>
+        <v>5.073828348551419</v>
       </c>
       <c r="D6" t="n">
-        <v>4.631316851653938</v>
+        <v>0.2028242187617373</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1362989576572911</v>
+        <v>0.003783973571307417</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>160.1374851976115</v>
+        <v>203.0457747057284</v>
       </c>
       <c r="H6" t="n">
-        <v>199.4972526483417</v>
+        <v>102.6348062425755</v>
       </c>
       <c r="I6" t="n">
-        <v>183.430394755112</v>
+        <v>134.1890534089342</v>
       </c>
       <c r="J6" t="n">
-        <v>241.711525274946</v>
+        <v>323.3941416316508</v>
       </c>
       <c r="K6" t="n">
-        <v>379.3637988858356</v>
+        <v>194.0390985245222</v>
       </c>
       <c r="L6" t="n">
-        <v>345.8556050598332</v>
+        <v>459.24388744721</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.014688373348133e-15</v>
+        <v>9.780957829962677e-17</v>
       </c>
       <c r="B7" t="n">
-        <v>-30.57030797746024</v>
+        <v>-8.714835450147174</v>
       </c>
       <c r="C7" t="n">
-        <v>-31.23457131638467</v>
+        <v>-5.073926494032001</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.623845117484152</v>
+        <v>-0.202932551570449</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2973545598157386</v>
+        <v>0.005647533378655745</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>342.7813656293661</v>
+        <v>209.1811638258204</v>
       </c>
       <c r="H7" t="n">
-        <v>183.1703678437171</v>
+        <v>264.6011480012432</v>
       </c>
       <c r="I7" t="n">
-        <v>292.7876326550343</v>
+        <v>143.6996660999505</v>
       </c>
       <c r="J7" t="n">
-        <v>427.4767156303036</v>
+        <v>269.6116397426714</v>
       </c>
       <c r="K7" t="n">
-        <v>307.5621396938427</v>
+        <v>336.58436347155</v>
       </c>
       <c r="L7" t="n">
-        <v>342.8459931841588</v>
+        <v>206.0342853507156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8.229926309129317e-17</v>
+        <v>-1.092429492735409e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>-27.66605975679562</v>
+        <v>13.85418898014175</v>
       </c>
       <c r="C8" t="n">
-        <v>1.067647483400888</v>
+        <v>1.16787605292904</v>
       </c>
       <c r="D8" t="n">
-        <v>4.633267345186171</v>
+        <v>0.2031241998160949</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01674395573535175</v>
+        <v>0.0006447783890831559</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>244.8777788044186</v>
+        <v>114.651205812829</v>
       </c>
       <c r="H8" t="n">
-        <v>414.586869905781</v>
+        <v>252.8297301668283</v>
       </c>
       <c r="I8" t="n">
-        <v>198.9677921464707</v>
+        <v>323.0668816220197</v>
       </c>
       <c r="J8" t="n">
-        <v>193.4914271019785</v>
+        <v>357.506875532349</v>
       </c>
       <c r="K8" t="n">
-        <v>175.1605859195013</v>
+        <v>327.965826704513</v>
       </c>
       <c r="L8" t="n">
-        <v>271.7000874512382</v>
+        <v>194.9570618870869</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.66682269851009e-17</v>
+        <v>3.633665321794214e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>-42.42638830924984</v>
+        <v>11.01893040258089</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.03506969916373</v>
+        <v>-1.671335538621919</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.633474617794199</v>
+        <v>-0.2031258266151972</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.004670479181094366</v>
+        <v>1.785955698459928e-05</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>252.3577601870796</v>
+        <v>110.8629981366128</v>
       </c>
       <c r="H9" t="n">
-        <v>386.1080042037839</v>
+        <v>245.1752277991199</v>
       </c>
       <c r="I9" t="n">
-        <v>377.0751564747108</v>
+        <v>328.1722045891901</v>
       </c>
       <c r="J9" t="n">
-        <v>464.6846390562647</v>
+        <v>284.4744390318555</v>
       </c>
       <c r="K9" t="n">
-        <v>232.7650087767408</v>
+        <v>193.9427140627287</v>
       </c>
       <c r="L9" t="n">
-        <v>220.7429079866505</v>
+        <v>200.6697782694127</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.289258457479122e-16</v>
+        <v>-5.533198564341929e-17</v>
       </c>
       <c r="B10" t="n">
-        <v>11.17117782101327</v>
+        <v>-0.9036399014302505</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.98828482354696</v>
+        <v>-2.837660219235009</v>
       </c>
       <c r="D10" t="n">
-        <v>4.617457403845774</v>
+        <v>-0.202955857918495</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3845803842123143</v>
+        <v>0.007829107217133075</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>327.4294104484989</v>
+        <v>255.913621478517</v>
       </c>
       <c r="H10" t="n">
-        <v>453.5492980307675</v>
+        <v>100.8931057727081</v>
       </c>
       <c r="I10" t="n">
-        <v>224.241542422005</v>
+        <v>209.1788911638618</v>
       </c>
       <c r="J10" t="n">
-        <v>224.0119019676069</v>
+        <v>285.8723420455359</v>
       </c>
       <c r="K10" t="n">
-        <v>328.0292642692195</v>
+        <v>326.09318403669</v>
       </c>
       <c r="L10" t="n">
-        <v>317.79303542216</v>
+        <v>419.7118462622228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8.882522817996928e-16</v>
+        <v>1.34276375726807e-16</v>
       </c>
       <c r="B11" t="n">
-        <v>-43.51395682176951</v>
+        <v>13.07169040182325</v>
       </c>
       <c r="C11" t="n">
-        <v>-29.97595638852331</v>
+        <v>0.268269752459522</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.61627346876385</v>
+        <v>-0.2029426073998401</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3844803120888034</v>
+        <v>-0.007829962003179071</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>431.454502347732</v>
+        <v>208.6496598163382</v>
       </c>
       <c r="H11" t="n">
-        <v>292.391012321192</v>
+        <v>202.1031213230056</v>
       </c>
       <c r="I11" t="n">
-        <v>268.4439002683727</v>
+        <v>336.6542068903365</v>
       </c>
       <c r="J11" t="n">
-        <v>425.3246468850106</v>
+        <v>130.8770012158401</v>
       </c>
       <c r="K11" t="n">
-        <v>367.9640033327566</v>
+        <v>326.1222458366921</v>
       </c>
       <c r="L11" t="n">
-        <v>198.9453684981033</v>
+        <v>352.7968951663149</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>300.1896575890655</v>
+        <v>159.8503687078877</v>
       </c>
       <c r="H12" t="n">
-        <v>460.4727091357807</v>
+        <v>187.48301332285</v>
       </c>
       <c r="I12" t="n">
-        <v>451.4362730085228</v>
+        <v>275.264103761584</v>
       </c>
       <c r="J12" t="n">
-        <v>175.3441372842708</v>
+        <v>236.1521574881101</v>
       </c>
       <c r="K12" t="n">
-        <v>247.3971304394904</v>
+        <v>447.90928881386</v>
       </c>
       <c r="L12" t="n">
-        <v>446.2664022331443</v>
+        <v>181.5026740474309</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>300.1896575890655</v>
+        <v>159.8503687078877</v>
       </c>
       <c r="H13" t="n">
-        <v>460.4727091357807</v>
+        <v>187.48301332285</v>
       </c>
       <c r="I13" t="n">
-        <v>451.4362730085228</v>
+        <v>275.264103761584</v>
       </c>
       <c r="J13" t="n">
-        <v>175.3441372842708</v>
+        <v>236.1521574881101</v>
       </c>
       <c r="K13" t="n">
-        <v>247.3971304394904</v>
+        <v>447.90928881386</v>
       </c>
       <c r="L13" t="n">
-        <v>446.2664022331443</v>
+        <v>181.5026740474309</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9.940793884389218e-15</v>
+        <v>4.333519793092376e-16</v>
       </c>
       <c r="B15" t="n">
-        <v>66.02934538380599</v>
+        <v>18.22655570992734</v>
       </c>
       <c r="C15" t="n">
-        <v>31.23460795245</v>
+        <v>5.073828348551419</v>
       </c>
       <c r="D15" t="n">
-        <v>4.633267345186171</v>
+        <v>0.2031241998160949</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3845803842123143</v>
+        <v>0.007829107217133075</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,458 +480,458 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.333519793092376e-16</v>
+        <v>5.22721939457294e-15</v>
       </c>
       <c r="B2" t="n">
-        <v>14.32970207851291</v>
+        <v>30.06645133516072</v>
       </c>
       <c r="C2" t="n">
-        <v>3.866825595790485</v>
+        <v>15.41316595702082</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1867912526209001</v>
+        <v>5.499049262682917</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008579083623691486</v>
+        <v>-0.03591399010017125</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.8952622243621946</v>
       </c>
       <c r="G2" t="n">
-        <v>155.239055293018</v>
+        <v>161.8384480408196</v>
       </c>
       <c r="H2" t="n">
-        <v>268.7996574166283</v>
+        <v>125.220320322053</v>
       </c>
       <c r="I2" t="n">
-        <v>120.7042447589839</v>
+        <v>305.1915522490676</v>
       </c>
       <c r="J2" t="n">
-        <v>232.2635270345889</v>
+        <v>181.8882076851612</v>
       </c>
       <c r="K2" t="n">
-        <v>324.7167866562738</v>
+        <v>317.0375021962662</v>
       </c>
       <c r="L2" t="n">
-        <v>172.3554033854167</v>
+        <v>374.703450668515</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-4.626097186756907e-16</v>
+        <v>-6.204413142870467e-15</v>
       </c>
       <c r="B3" t="n">
-        <v>3.32380072754209</v>
+        <v>29.2197331618613</v>
       </c>
       <c r="C3" t="n">
-        <v>-3.612831347902668</v>
+        <v>15.23952006267491</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01203443264648458</v>
+        <v>3.880025475954377</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0005248379813055048</v>
+        <v>-0.4453597708064225</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.3298792650022951</v>
       </c>
       <c r="G3" t="n">
-        <v>126.298814844755</v>
+        <v>226.3340446830927</v>
       </c>
       <c r="H3" t="n">
-        <v>216.0676442175127</v>
+        <v>222.5272066889487</v>
       </c>
       <c r="I3" t="n">
-        <v>289.4538859265093</v>
+        <v>248.9685265380324</v>
       </c>
       <c r="J3" t="n">
-        <v>252.8933605583935</v>
+        <v>297.9954591804341</v>
       </c>
       <c r="K3" t="n">
-        <v>224.8385547745061</v>
+        <v>359.1705085651125</v>
       </c>
       <c r="L3" t="n">
-        <v>338.8836419862683</v>
+        <v>320.8349058227885</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.831630857015175e-18</v>
+        <v>1.863956007164518e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>18.22655570992734</v>
+        <v>32.05417989061412</v>
       </c>
       <c r="C4" t="n">
-        <v>5.055743683585101</v>
+        <v>17.30581623876991</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1955330917041322</v>
+        <v>5.66298790405206</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.007530158502224977</v>
+        <v>0.3178325223310227</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.027399130741283</v>
       </c>
       <c r="G4" t="n">
-        <v>219.2313331751081</v>
+        <v>152.5727020577027</v>
       </c>
       <c r="H4" t="n">
-        <v>128.9995092647846</v>
+        <v>179.6064074381231</v>
       </c>
       <c r="I4" t="n">
-        <v>354.1295950808803</v>
+        <v>184.5045088657856</v>
       </c>
       <c r="J4" t="n">
-        <v>328.1288015049099</v>
+        <v>202.8836748547632</v>
       </c>
       <c r="K4" t="n">
-        <v>299.5968285520432</v>
+        <v>382.5681632395902</v>
       </c>
       <c r="L4" t="n">
-        <v>398.84889378004</v>
+        <v>431.38616872405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.660676677639394e-17</v>
+        <v>-3.223952492679939e-16</v>
       </c>
       <c r="B5" t="n">
-        <v>-9.122017648126123</v>
+        <v>-18.7786118921718</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.057369306583921</v>
+        <v>-17.25829449094056</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1961165214039462</v>
+        <v>-5.610528988961049</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00712352314118656</v>
+        <v>-0.1056833698240374</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.07239583186859895</v>
       </c>
       <c r="G5" t="n">
-        <v>94.73192944856265</v>
+        <v>124.3797192343261</v>
       </c>
       <c r="H5" t="n">
-        <v>164.9460680543654</v>
+        <v>256.3463377120632</v>
       </c>
       <c r="I5" t="n">
-        <v>276.7068012752046</v>
+        <v>140.6951223478019</v>
       </c>
       <c r="J5" t="n">
-        <v>209.4676251409578</v>
+        <v>212.7827444496326</v>
       </c>
       <c r="K5" t="n">
-        <v>251.6464575009193</v>
+        <v>443.4863764774395</v>
       </c>
       <c r="L5" t="n">
-        <v>187.6528711351712</v>
+        <v>189.3947636895273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-6.465077602175565e-17</v>
+        <v>3.927569625436954e-15</v>
       </c>
       <c r="B6" t="n">
-        <v>12.54266116535535</v>
+        <v>31.50570731830327</v>
       </c>
       <c r="C6" t="n">
-        <v>5.073828348551419</v>
+        <v>17.35261166109319</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2028242187617373</v>
+        <v>5.717188834642265</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003783973571307417</v>
+        <v>0.1736320610571605</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.7681607542222185</v>
       </c>
       <c r="G6" t="n">
-        <v>203.0457747057284</v>
+        <v>266.1201092733139</v>
       </c>
       <c r="H6" t="n">
-        <v>102.6348062425755</v>
+        <v>177.8712816698976</v>
       </c>
       <c r="I6" t="n">
-        <v>134.1890534089342</v>
+        <v>318.3118059139827</v>
       </c>
       <c r="J6" t="n">
-        <v>323.3941416316508</v>
+        <v>206.9325164888696</v>
       </c>
       <c r="K6" t="n">
-        <v>194.0390985245222</v>
+        <v>429.4411652083476</v>
       </c>
       <c r="L6" t="n">
-        <v>459.24388744721</v>
+        <v>164.162599667304</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9.780957829962677e-17</v>
+        <v>3.603874487490234e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>-8.714835450147174</v>
+        <v>-8.619480675057829</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.073926494032001</v>
+        <v>-17.34744887786591</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.202932551570449</v>
+        <v>-5.714493936043996</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005647533378655745</v>
+        <v>-0.09907266370022728</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.03419362818375037</v>
       </c>
       <c r="G7" t="n">
-        <v>209.1811638258204</v>
+        <v>235.1385410379251</v>
       </c>
       <c r="H7" t="n">
-        <v>264.6011480012432</v>
+        <v>117.7234282677895</v>
       </c>
       <c r="I7" t="n">
-        <v>143.6996660999505</v>
+        <v>354.1582222563849</v>
       </c>
       <c r="J7" t="n">
-        <v>269.6116397426714</v>
+        <v>267.1660615540334</v>
       </c>
       <c r="K7" t="n">
-        <v>336.58436347155</v>
+        <v>287.4459374985538</v>
       </c>
       <c r="L7" t="n">
-        <v>206.0342853507156</v>
+        <v>414.1224681168188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.092429492735409e-16</v>
+        <v>-4.265235481223306e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85418898014175</v>
+        <v>30.20354364453306</v>
       </c>
       <c r="C8" t="n">
-        <v>1.16787605292904</v>
+        <v>15.66575085829385</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2031241998160949</v>
+        <v>5.725802194098393</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0006447783890831559</v>
+        <v>-0.05466210476450293</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.281370729313177</v>
       </c>
       <c r="G8" t="n">
-        <v>114.651205812829</v>
+        <v>214.2290962063973</v>
       </c>
       <c r="H8" t="n">
-        <v>252.8297301668283</v>
+        <v>210.4292745325691</v>
       </c>
       <c r="I8" t="n">
-        <v>323.0668816220197</v>
+        <v>154.5162790498206</v>
       </c>
       <c r="J8" t="n">
-        <v>357.506875532349</v>
+        <v>122.8354935177448</v>
       </c>
       <c r="K8" t="n">
-        <v>327.965826704513</v>
+        <v>210.1991076848735</v>
       </c>
       <c r="L8" t="n">
-        <v>194.9570618870869</v>
+        <v>469.7229076893103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.633665321794214e-17</v>
+        <v>1.954424059435197e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>11.01893040258089</v>
+        <v>-1.493950123935396</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.671335538621919</v>
+        <v>-16.24211173961427</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2031258266151972</v>
+        <v>-5.726854380130433</v>
       </c>
       <c r="E9" t="n">
-        <v>1.785955698459928e-05</v>
+        <v>0.02955003778623009</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.02051080834873126</v>
       </c>
       <c r="G9" t="n">
-        <v>110.8629981366128</v>
+        <v>175.6593800771513</v>
       </c>
       <c r="H9" t="n">
-        <v>245.1752277991199</v>
+        <v>172.0168565498477</v>
       </c>
       <c r="I9" t="n">
-        <v>328.1722045891901</v>
+        <v>133.736916633457</v>
       </c>
       <c r="J9" t="n">
-        <v>284.4744390318555</v>
+        <v>243.2419600012682</v>
       </c>
       <c r="K9" t="n">
-        <v>193.9427140627287</v>
+        <v>241.1794543497848</v>
       </c>
       <c r="L9" t="n">
-        <v>200.6697782694127</v>
+        <v>235.8164765237252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-5.533198564341929e-17</v>
+        <v>4.716377109975007e-16</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.9036399014302505</v>
+        <v>-6.802626014172191</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.837660219235009</v>
+        <v>-15.59789541128376</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.202955857918495</v>
+        <v>-4.662538873505761</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007829107217133075</v>
+        <v>1.157456477631696</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.01055761013205708</v>
       </c>
       <c r="G10" t="n">
-        <v>255.913621478517</v>
+        <v>127.370609012779</v>
       </c>
       <c r="H10" t="n">
-        <v>100.8931057727081</v>
+        <v>149.8294035551225</v>
       </c>
       <c r="I10" t="n">
-        <v>209.1788911638618</v>
+        <v>340.433793531568</v>
       </c>
       <c r="J10" t="n">
-        <v>285.8723420455359</v>
+        <v>347.8127476809043</v>
       </c>
       <c r="K10" t="n">
-        <v>326.09318403669</v>
+        <v>241.1023444973202</v>
       </c>
       <c r="L10" t="n">
-        <v>419.7118462622228</v>
+        <v>182.0130276525776</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.34276375726807e-16</v>
+        <v>1.207217266449696e-16</v>
       </c>
       <c r="B11" t="n">
-        <v>13.07169040182325</v>
+        <v>-1.654728177146368</v>
       </c>
       <c r="C11" t="n">
-        <v>0.268269752459522</v>
+        <v>-3.284385825672477</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2029426073998401</v>
+        <v>4.615263030867897</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007829962003179071</v>
+        <v>-1.161557722577218</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0.04622155033688857</v>
       </c>
       <c r="G11" t="n">
-        <v>208.6496598163382</v>
+        <v>260.0808046287351</v>
       </c>
       <c r="H11" t="n">
-        <v>202.1031213230056</v>
+        <v>156.5454095064879</v>
       </c>
       <c r="I11" t="n">
-        <v>336.6542068903365</v>
+        <v>149.7946757665298</v>
       </c>
       <c r="J11" t="n">
-        <v>130.8770012158401</v>
+        <v>159.597325853146</v>
       </c>
       <c r="K11" t="n">
-        <v>326.1222458366921</v>
+        <v>479.6722043662787</v>
       </c>
       <c r="L11" t="n">
-        <v>352.7968951663149</v>
+        <v>336.6261433229088</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>6.528211799254328e-16</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>3.408851763964884</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-9.005323204467899</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2.631560079710766</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.318796193867298</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.096694142712799</v>
       </c>
       <c r="G12" t="n">
-        <v>159.8503687078877</v>
+        <v>220.8706434958923</v>
       </c>
       <c r="H12" t="n">
-        <v>187.48301332285</v>
+        <v>236.73461293662</v>
       </c>
       <c r="I12" t="n">
-        <v>275.264103761584</v>
+        <v>353.819113003415</v>
       </c>
       <c r="J12" t="n">
-        <v>236.1521574881101</v>
+        <v>179.303329809043</v>
       </c>
       <c r="K12" t="n">
-        <v>447.90928881386</v>
+        <v>235.6382834868263</v>
       </c>
       <c r="L12" t="n">
-        <v>181.5026740474309</v>
+        <v>466.5163839230927</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-5.138086314245116e-16</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>24.24524056951606</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>9.698230191316881</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-1.942114966058404</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.2558737290546119</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-1.096783998556189</v>
       </c>
       <c r="G13" t="n">
-        <v>159.8503687078877</v>
+        <v>179.3382823031419</v>
       </c>
       <c r="H13" t="n">
-        <v>187.48301332285</v>
+        <v>257.7483544694285</v>
       </c>
       <c r="I13" t="n">
-        <v>275.264103761584</v>
+        <v>287.4560432481327</v>
       </c>
       <c r="J13" t="n">
-        <v>236.1521574881101</v>
+        <v>347.5738154698854</v>
       </c>
       <c r="K13" t="n">
-        <v>447.90928881386</v>
+        <v>308.4261324928663</v>
       </c>
       <c r="L13" t="n">
-        <v>181.5026740474309</v>
+        <v>183.5374916800037</v>
       </c>
     </row>
     <row r="14">
@@ -968,22 +968,22 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.333519793092376e-16</v>
+        <v>5.22721939457294e-15</v>
       </c>
       <c r="B15" t="n">
-        <v>18.22655570992734</v>
+        <v>32.05417989061412</v>
       </c>
       <c r="C15" t="n">
-        <v>5.073828348551419</v>
+        <v>17.35261166109319</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2031241998160949</v>
+        <v>5.725802194098393</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007829107217133075</v>
+        <v>1.157456477631696</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.096694142712799</v>
       </c>
     </row>
   </sheetData>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,458 +480,458 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.22721939457294e-15</v>
+        <v>4.79424310448062e-15</v>
       </c>
       <c r="B2" t="n">
-        <v>30.06645133516072</v>
+        <v>25.71510959999178</v>
       </c>
       <c r="C2" t="n">
-        <v>15.41316595702082</v>
+        <v>10.98155828636764</v>
       </c>
       <c r="D2" t="n">
-        <v>5.499049262682917</v>
+        <v>4.374477620662944</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03591399010017125</v>
+        <v>0.2645002492948682</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8952622243621946</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>161.8384480408196</v>
+        <v>142.0024015737405</v>
       </c>
       <c r="H2" t="n">
-        <v>125.220320322053</v>
+        <v>262.1312136074099</v>
       </c>
       <c r="I2" t="n">
-        <v>305.1915522490676</v>
+        <v>254.5847404413345</v>
       </c>
       <c r="J2" t="n">
-        <v>181.8882076851612</v>
+        <v>123.6712318816544</v>
       </c>
       <c r="K2" t="n">
-        <v>317.0375021962662</v>
+        <v>394.5588590159977</v>
       </c>
       <c r="L2" t="n">
-        <v>374.703450668515</v>
+        <v>232.968549019461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-6.204413142870467e-15</v>
+        <v>-4.713345280855158e-15</v>
       </c>
       <c r="B3" t="n">
-        <v>29.2197331618613</v>
+        <v>28.18687417747587</v>
       </c>
       <c r="C3" t="n">
-        <v>15.23952006267491</v>
+        <v>13.53095195972411</v>
       </c>
       <c r="D3" t="n">
-        <v>3.880025475954377</v>
+        <v>3.786823911277072</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4453597708064225</v>
+        <v>-0.267706859823079</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3298792650022951</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>226.3340446830927</v>
+        <v>227.4082662026733</v>
       </c>
       <c r="H3" t="n">
-        <v>222.5272066889487</v>
+        <v>120.6164730315904</v>
       </c>
       <c r="I3" t="n">
-        <v>248.9685265380324</v>
+        <v>345.8789662776776</v>
       </c>
       <c r="J3" t="n">
-        <v>297.9954591804341</v>
+        <v>347.8804493463169</v>
       </c>
       <c r="K3" t="n">
-        <v>359.1705085651125</v>
+        <v>178.4500130869134</v>
       </c>
       <c r="L3" t="n">
-        <v>320.8349058227885</v>
+        <v>198.2447196872965</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.863956007164518e-16</v>
+        <v>1.510144327357817e-15</v>
       </c>
       <c r="B4" t="n">
-        <v>32.05417989061412</v>
+        <v>31.00848975065441</v>
       </c>
       <c r="C4" t="n">
-        <v>17.30581623876991</v>
+        <v>16.25899839760373</v>
       </c>
       <c r="D4" t="n">
-        <v>5.66298790405206</v>
+        <v>4.625085901303157</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3178325223310227</v>
+        <v>0.2379074566233839</v>
       </c>
       <c r="F4" t="n">
-        <v>1.027399130741283</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>152.5727020577027</v>
+        <v>170.7978482883737</v>
       </c>
       <c r="H4" t="n">
-        <v>179.6064074381231</v>
+        <v>112.3422003149831</v>
       </c>
       <c r="I4" t="n">
-        <v>184.5045088657856</v>
+        <v>160.276625316054</v>
       </c>
       <c r="J4" t="n">
-        <v>202.8836748547632</v>
+        <v>135.8257052214192</v>
       </c>
       <c r="K4" t="n">
-        <v>382.5681632395902</v>
+        <v>229.486610082558</v>
       </c>
       <c r="L4" t="n">
-        <v>431.38616872405</v>
+        <v>338.2416148356492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-3.223952492679939e-16</v>
+        <v>-2.282389201370052e-17</v>
       </c>
       <c r="B5" t="n">
-        <v>-18.7786118921718</v>
+        <v>-17.76747560228679</v>
       </c>
       <c r="C5" t="n">
-        <v>-17.25829449094056</v>
+        <v>-16.23846767717408</v>
       </c>
       <c r="D5" t="n">
-        <v>-5.610528988961049</v>
+        <v>-4.616357419291472</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1056833698240374</v>
+        <v>-0.1485028013447443</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07239583186859895</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>124.3797192343261</v>
+        <v>204.97839967806</v>
       </c>
       <c r="H5" t="n">
-        <v>256.3463377120632</v>
+        <v>239.8626357275546</v>
       </c>
       <c r="I5" t="n">
-        <v>140.6951223478019</v>
+        <v>302.1516993262788</v>
       </c>
       <c r="J5" t="n">
-        <v>212.7827444496326</v>
+        <v>247.0017198963548</v>
       </c>
       <c r="K5" t="n">
-        <v>443.4863764774395</v>
+        <v>275.1510299637725</v>
       </c>
       <c r="L5" t="n">
-        <v>189.3947636895273</v>
+        <v>285.946030284656</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3.927569625436954e-15</v>
+        <v>-3.15589693428011e-16</v>
       </c>
       <c r="B6" t="n">
-        <v>31.50570731830327</v>
+        <v>18.41674251498214</v>
       </c>
       <c r="C6" t="n">
-        <v>17.35261166109319</v>
+        <v>16.27205235351061</v>
       </c>
       <c r="D6" t="n">
-        <v>5.717188834642265</v>
+        <v>4.632633678546839</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1736320610571605</v>
+        <v>-0.001251015459573803</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7681607542222185</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>266.1201092733139</v>
+        <v>261.1058062226845</v>
       </c>
       <c r="H6" t="n">
-        <v>177.8712816698976</v>
+        <v>128.9843913884479</v>
       </c>
       <c r="I6" t="n">
-        <v>318.3118059139827</v>
+        <v>183.8545148370071</v>
       </c>
       <c r="J6" t="n">
-        <v>206.9325164888696</v>
+        <v>274.745948431239</v>
       </c>
       <c r="K6" t="n">
-        <v>429.4411652083476</v>
+        <v>421.3315158731816</v>
       </c>
       <c r="L6" t="n">
-        <v>164.162599667304</v>
+        <v>316.7233604498612</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.603874487490234e-16</v>
+        <v>1.68786011801201e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>-8.619480675057829</v>
+        <v>-4.496042422036107</v>
       </c>
       <c r="C7" t="n">
-        <v>-17.34744887786591</v>
+        <v>-16.27530023370538</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.714493936043996</v>
+        <v>-4.627999962839061</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09907266370022728</v>
+        <v>-0.1131238104503505</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03419362818375037</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>235.1385410379251</v>
+        <v>220.9252896166192</v>
       </c>
       <c r="H7" t="n">
-        <v>117.7234282677895</v>
+        <v>256.6821420088158</v>
       </c>
       <c r="I7" t="n">
-        <v>354.1582222563849</v>
+        <v>264.5616980104102</v>
       </c>
       <c r="J7" t="n">
-        <v>267.1660615540334</v>
+        <v>181.2431254356332</v>
       </c>
       <c r="K7" t="n">
-        <v>287.4459374985538</v>
+        <v>337.5959443350316</v>
       </c>
       <c r="L7" t="n">
-        <v>414.1224681168188</v>
+        <v>218.6708713180642</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-4.265235481223306e-16</v>
+        <v>-4.467017853133482e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>30.20354364453306</v>
+        <v>21.71491494547913</v>
       </c>
       <c r="C8" t="n">
-        <v>15.66575085829385</v>
+        <v>14.30278125438425</v>
       </c>
       <c r="D8" t="n">
-        <v>5.725802194098393</v>
+        <v>4.633438747396424</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.05466210476450293</v>
+        <v>-0.002665496749821603</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.281370729313177</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>214.2290962063973</v>
+        <v>103.533069763736</v>
       </c>
       <c r="H8" t="n">
-        <v>210.4292745325691</v>
+        <v>234.3542013025498</v>
       </c>
       <c r="I8" t="n">
-        <v>154.5162790498206</v>
+        <v>291.0687383969557</v>
       </c>
       <c r="J8" t="n">
-        <v>122.8354935177448</v>
+        <v>170.8877817866389</v>
       </c>
       <c r="K8" t="n">
-        <v>210.1991076848735</v>
+        <v>354.2320055995164</v>
       </c>
       <c r="L8" t="n">
-        <v>469.7229076893103</v>
+        <v>451.9456307114276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.954424059435197e-17</v>
+        <v>-4.460023680897637e-16</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.493950123935396</v>
+        <v>-10.91003501548226</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.24211173961427</v>
+        <v>-9.777929575895707</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.726854380130433</v>
+        <v>-4.633468822541198</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02955003778623009</v>
+        <v>-0.004337789022658932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02051080834873126</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>175.6593800771513</v>
+        <v>239.0309013316068</v>
       </c>
       <c r="H9" t="n">
-        <v>172.0168565498477</v>
+        <v>102.5845242805259</v>
       </c>
       <c r="I9" t="n">
-        <v>133.736916633457</v>
+        <v>270.3055550128322</v>
       </c>
       <c r="J9" t="n">
-        <v>243.2419600012682</v>
+        <v>211.9504225209743</v>
       </c>
       <c r="K9" t="n">
-        <v>241.1794543497848</v>
+        <v>203.1576293470825</v>
       </c>
       <c r="L9" t="n">
-        <v>235.8164765237252</v>
+        <v>290.827930159556</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4.716377109975007e-16</v>
+        <v>-3.525086161867811e-16</v>
       </c>
       <c r="B10" t="n">
-        <v>-6.802626014172191</v>
+        <v>1.495624595222779</v>
       </c>
       <c r="C10" t="n">
-        <v>-15.59789541128376</v>
+        <v>-13.01917802643402</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.662538873505761</v>
+        <v>-4.617418066657385</v>
       </c>
       <c r="E10" t="n">
-        <v>1.157456477631696</v>
+        <v>0.3845763708362961</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01055761013205708</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>127.370609012779</v>
+        <v>159.2880131147132</v>
       </c>
       <c r="H10" t="n">
-        <v>149.8294035551225</v>
+        <v>131.3379658326807</v>
       </c>
       <c r="I10" t="n">
-        <v>340.433793531568</v>
+        <v>277.0106815269705</v>
       </c>
       <c r="J10" t="n">
-        <v>347.8127476809043</v>
+        <v>321.781139728988</v>
       </c>
       <c r="K10" t="n">
-        <v>241.1023444973202</v>
+        <v>185.6571318980791</v>
       </c>
       <c r="L10" t="n">
-        <v>182.0130276525776</v>
+        <v>457.2760843890496</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.207217266449696e-16</v>
+        <v>7.386813006228796e-18</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.654728177146368</v>
+        <v>10.99942658161119</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.284385825672477</v>
+        <v>-2.342902193428436</v>
       </c>
       <c r="D11" t="n">
-        <v>4.615263030867897</v>
+        <v>-4.617190969457243</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.161557722577218</v>
+        <v>-0.3845216165390186</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.04622155033688857</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>260.0808046287351</v>
+        <v>128.571442951567</v>
       </c>
       <c r="H11" t="n">
-        <v>156.5454095064879</v>
+        <v>202.5922415688224</v>
       </c>
       <c r="I11" t="n">
-        <v>149.7946757665298</v>
+        <v>255.3338383116172</v>
       </c>
       <c r="J11" t="n">
-        <v>159.597325853146</v>
+        <v>285.766643067511</v>
       </c>
       <c r="K11" t="n">
-        <v>479.6722043662787</v>
+        <v>440.0129011369125</v>
       </c>
       <c r="L11" t="n">
-        <v>336.6261433229088</v>
+        <v>298.1036585000783</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6.528211799254328e-16</v>
+        <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>3.408851763964884</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-9.005323204467899</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2.631560079710766</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.318796193867298</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.096694142712799</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>220.8706434958923</v>
+        <v>90.49711257789424</v>
       </c>
       <c r="H12" t="n">
-        <v>236.73461293662</v>
+        <v>229.9735274098612</v>
       </c>
       <c r="I12" t="n">
-        <v>353.819113003415</v>
+        <v>279.2062147166107</v>
       </c>
       <c r="J12" t="n">
-        <v>179.303329809043</v>
+        <v>337.2787245425917</v>
       </c>
       <c r="K12" t="n">
-        <v>235.6382834868263</v>
+        <v>173.3836478329517</v>
       </c>
       <c r="L12" t="n">
-        <v>466.5163839230927</v>
+        <v>183.1392334432057</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-5.138086314245116e-16</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>24.24524056951606</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.698230191316881</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.942114966058404</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2558737290546119</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.096783998556189</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>179.3382823031419</v>
+        <v>90.49711257789424</v>
       </c>
       <c r="H13" t="n">
-        <v>257.7483544694285</v>
+        <v>229.9735274098612</v>
       </c>
       <c r="I13" t="n">
-        <v>287.4560432481327</v>
+        <v>279.2062147166107</v>
       </c>
       <c r="J13" t="n">
-        <v>347.5738154698854</v>
+        <v>337.2787245425917</v>
       </c>
       <c r="K13" t="n">
-        <v>308.4261324928663</v>
+        <v>173.3836478329517</v>
       </c>
       <c r="L13" t="n">
-        <v>183.5374916800037</v>
+        <v>183.1392334432057</v>
       </c>
     </row>
     <row r="14">
@@ -968,22 +968,22 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5.22721939457294e-15</v>
+        <v>4.79424310448062e-15</v>
       </c>
       <c r="B15" t="n">
-        <v>32.05417989061412</v>
+        <v>31.00848975065441</v>
       </c>
       <c r="C15" t="n">
-        <v>17.35261166109319</v>
+        <v>16.27205235351061</v>
       </c>
       <c r="D15" t="n">
-        <v>5.725802194098393</v>
+        <v>4.633438747396424</v>
       </c>
       <c r="E15" t="n">
-        <v>1.157456477631696</v>
+        <v>0.3845763708362961</v>
       </c>
       <c r="F15" t="n">
-        <v>1.096694142712799</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.79424310448062e-15</v>
+        <v>3.896714452764359e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>25.71510959999178</v>
+        <v>2.737554051798655</v>
       </c>
       <c r="C2" t="n">
-        <v>10.98155828636764</v>
+        <v>0.06986409927382436</v>
       </c>
       <c r="D2" t="n">
-        <v>4.374477620662944</v>
+        <v>-0.1602253121937256</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2645002492948682</v>
+        <v>-0.002757997913445265</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>142.0024015737405</v>
+        <v>139.1624692475139</v>
       </c>
       <c r="H2" t="n">
-        <v>262.1312136074099</v>
+        <v>106.101773727676</v>
       </c>
       <c r="I2" t="n">
-        <v>254.5847404413345</v>
+        <v>277.4607960838766</v>
       </c>
       <c r="J2" t="n">
-        <v>123.6712318816544</v>
+        <v>183.5356138239177</v>
       </c>
       <c r="K2" t="n">
-        <v>394.5588590159977</v>
+        <v>300.2555102547457</v>
       </c>
       <c r="L2" t="n">
-        <v>232.968549019461</v>
+        <v>418.9762708994894</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-4.713345280855158e-15</v>
+        <v>-3.295355185473915e-16</v>
       </c>
       <c r="B3" t="n">
-        <v>28.18687417747587</v>
+        <v>5.497067341572366</v>
       </c>
       <c r="C3" t="n">
-        <v>13.53095195972411</v>
+        <v>0.932378557680911</v>
       </c>
       <c r="D3" t="n">
-        <v>3.786823911277072</v>
+        <v>-0.07674321454966482</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.267706859823079</v>
+        <v>0.002251653634490288</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>227.4082662026733</v>
+        <v>222.8439743021924</v>
       </c>
       <c r="H3" t="n">
-        <v>120.6164730315904</v>
+        <v>226.1076609327292</v>
       </c>
       <c r="I3" t="n">
-        <v>345.8789662776776</v>
+        <v>159.6676690574295</v>
       </c>
       <c r="J3" t="n">
-        <v>347.8804493463169</v>
+        <v>359.6462063428085</v>
       </c>
       <c r="K3" t="n">
-        <v>178.4500130869134</v>
+        <v>241.6602823736781</v>
       </c>
       <c r="L3" t="n">
-        <v>198.2447196872965</v>
+        <v>261.1978359276691</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.510144327357817e-15</v>
+        <v>9.020282803053189e-19</v>
       </c>
       <c r="B4" t="n">
-        <v>31.00848975065441</v>
+        <v>7.267258419981797</v>
       </c>
       <c r="C4" t="n">
-        <v>16.25899839760373</v>
+        <v>2.158576295222186</v>
       </c>
       <c r="D4" t="n">
-        <v>4.625085901303157</v>
+        <v>0.1957796907205593</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2379074566233839</v>
+        <v>0.007255518498455599</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>170.7978482883737</v>
+        <v>95.14499516009055</v>
       </c>
       <c r="H4" t="n">
-        <v>112.3422003149831</v>
+        <v>233.9689608005009</v>
       </c>
       <c r="I4" t="n">
-        <v>160.276625316054</v>
+        <v>331.8563576416215</v>
       </c>
       <c r="J4" t="n">
-        <v>135.8257052214192</v>
+        <v>182.7442176710605</v>
       </c>
       <c r="K4" t="n">
-        <v>229.486610082558</v>
+        <v>312.7598149390951</v>
       </c>
       <c r="L4" t="n">
-        <v>338.2416148356492</v>
+        <v>289.7143745797266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-2.282389201370052e-17</v>
+        <v>-6.117474266014258e-17</v>
       </c>
       <c r="B5" t="n">
-        <v>-17.76747560228679</v>
+        <v>-3.633766504446859</v>
       </c>
       <c r="C5" t="n">
-        <v>-16.23846767717408</v>
+        <v>-2.131500906967353</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.616357419291472</v>
+        <v>-0.1688118667512442</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1485028013447443</v>
+        <v>0.002156390022992584</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>204.97839967806</v>
+        <v>217.6336834131148</v>
       </c>
       <c r="H5" t="n">
-        <v>239.8626357275546</v>
+        <v>224.5306576761033</v>
       </c>
       <c r="I5" t="n">
-        <v>302.1516993262788</v>
+        <v>261.6447977818998</v>
       </c>
       <c r="J5" t="n">
-        <v>247.0017198963548</v>
+        <v>292.1049828638553</v>
       </c>
       <c r="K5" t="n">
-        <v>275.1510299637725</v>
+        <v>241.779662896094</v>
       </c>
       <c r="L5" t="n">
-        <v>285.946030284656</v>
+        <v>355.1180756334485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-3.15589693428011e-16</v>
+        <v>-1.055930742908061e-17</v>
       </c>
       <c r="B6" t="n">
-        <v>18.41674251498214</v>
+        <v>6.173514705675393</v>
       </c>
       <c r="C6" t="n">
-        <v>16.27205235351061</v>
+        <v>2.172317485627652</v>
       </c>
       <c r="D6" t="n">
-        <v>4.632633678546839</v>
+        <v>0.2027027241466817</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001251015459573803</v>
+        <v>0.006636470843877285</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>261.1058062226845</v>
+        <v>153.6074935304167</v>
       </c>
       <c r="H6" t="n">
-        <v>128.9843913884479</v>
+        <v>226.9016543952538</v>
       </c>
       <c r="I6" t="n">
-        <v>183.8545148370071</v>
+        <v>336.470339540183</v>
       </c>
       <c r="J6" t="n">
-        <v>274.745948431239</v>
+        <v>258.0140376927241</v>
       </c>
       <c r="K6" t="n">
-        <v>421.3315158731816</v>
+        <v>470.5521282863169</v>
       </c>
       <c r="L6" t="n">
-        <v>316.7233604498612</v>
+        <v>405.6950453514312</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.68786011801201e-16</v>
+        <v>1.255896232806766e-17</v>
       </c>
       <c r="B7" t="n">
-        <v>-4.496042422036107</v>
+        <v>0.2051034198074366</v>
       </c>
       <c r="C7" t="n">
-        <v>-16.27530023370538</v>
+        <v>-2.172544866685358</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.627999962839061</v>
+        <v>-0.2029742037666173</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1131238104503505</v>
+        <v>0.007344350569165229</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>220.9252896166192</v>
+        <v>91.32774854755333</v>
       </c>
       <c r="H7" t="n">
-        <v>256.6821420088158</v>
+        <v>167.0767432473507</v>
       </c>
       <c r="I7" t="n">
-        <v>264.5616980104102</v>
+        <v>326.7948502760407</v>
       </c>
       <c r="J7" t="n">
-        <v>181.2431254356332</v>
+        <v>334.3775397079096</v>
       </c>
       <c r="K7" t="n">
-        <v>337.5959443350316</v>
+        <v>425.8000464268531</v>
       </c>
       <c r="L7" t="n">
-        <v>218.6708713180642</v>
+        <v>354.9993669547285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-4.467017853133482e-16</v>
+        <v>-1.085217845472576e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>21.71491494547913</v>
+        <v>4.800307518608793</v>
       </c>
       <c r="C8" t="n">
-        <v>14.30278125438425</v>
+        <v>-0.1355644008929682</v>
       </c>
       <c r="D8" t="n">
-        <v>4.633438747396424</v>
+        <v>0.2031218468440417</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.002665496749821603</v>
+        <v>-0.0003151999537749535</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>103.533069763736</v>
+        <v>130.4123435782047</v>
       </c>
       <c r="H8" t="n">
-        <v>234.3542013025498</v>
+        <v>221.7717244399619</v>
       </c>
       <c r="I8" t="n">
-        <v>291.0687383969557</v>
+        <v>213.1724318371147</v>
       </c>
       <c r="J8" t="n">
-        <v>170.8877817866389</v>
+        <v>234.7475776197601</v>
       </c>
       <c r="K8" t="n">
-        <v>354.2320055995164</v>
+        <v>169.2539968887581</v>
       </c>
       <c r="L8" t="n">
-        <v>451.9456307114276</v>
+        <v>210.4631843872227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-4.460023680897637e-16</v>
+        <v>-3.072499163359244e-18</v>
       </c>
       <c r="B9" t="n">
-        <v>-10.91003501548226</v>
+        <v>-0.9567436167784098</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.777929575895707</v>
+        <v>-1.945344244893715</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.633468822541198</v>
+        <v>-0.2031216631868815</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.004337789022658932</v>
+        <v>0.0007951444826114006</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>239.0309013316068</v>
+        <v>113.7575893067084</v>
       </c>
       <c r="H9" t="n">
-        <v>102.5845242805259</v>
+        <v>244.987381535725</v>
       </c>
       <c r="I9" t="n">
-        <v>270.3055550128322</v>
+        <v>341.588748707119</v>
       </c>
       <c r="J9" t="n">
-        <v>211.9504225209743</v>
+        <v>289.3378789733964</v>
       </c>
       <c r="K9" t="n">
-        <v>203.1576293470825</v>
+        <v>201.5798243302697</v>
       </c>
       <c r="L9" t="n">
-        <v>290.827930159556</v>
+        <v>202.5173681864425</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-3.525086161867811e-16</v>
+        <v>1.518219360788948e-17</v>
       </c>
       <c r="B10" t="n">
-        <v>1.495624595222779</v>
+        <v>2.967641730304288</v>
       </c>
       <c r="C10" t="n">
-        <v>-13.01917802643402</v>
+        <v>-2.097286627394027</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.617418066657385</v>
+        <v>-0.2029266557956295</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3845763708362961</v>
+        <v>0.007828880082645486</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>159.2880131147132</v>
+        <v>132.8769030567743</v>
       </c>
       <c r="H10" t="n">
-        <v>131.3379658326807</v>
+        <v>258.6872592810095</v>
       </c>
       <c r="I10" t="n">
-        <v>277.0106815269705</v>
+        <v>139.1130445947136</v>
       </c>
       <c r="J10" t="n">
-        <v>321.781139728988</v>
+        <v>292.157659285013</v>
       </c>
       <c r="K10" t="n">
-        <v>185.6571318980791</v>
+        <v>448.0945606398641</v>
       </c>
       <c r="L10" t="n">
-        <v>457.2760843890496</v>
+        <v>274.0920069477049</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7.386813006228796e-18</v>
+        <v>1.568269645545887e-17</v>
       </c>
       <c r="B11" t="n">
-        <v>10.99942658161119</v>
+        <v>5.695513254692193</v>
       </c>
       <c r="C11" t="n">
-        <v>-2.342902193428436</v>
+        <v>1.434949470147667</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.617190969457243</v>
+        <v>0.2029583521528772</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3845216165390186</v>
+        <v>-0.007830636951523761</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>128.571442951567</v>
+        <v>209.616503710768</v>
       </c>
       <c r="H11" t="n">
-        <v>202.5922415688224</v>
+        <v>126.9719853100555</v>
       </c>
       <c r="I11" t="n">
-        <v>255.3338383116172</v>
+        <v>263.0752389717435</v>
       </c>
       <c r="J11" t="n">
-        <v>285.766643067511</v>
+        <v>211.0447222529531</v>
       </c>
       <c r="K11" t="n">
-        <v>440.0129011369125</v>
+        <v>430.4404075677971</v>
       </c>
       <c r="L11" t="n">
-        <v>298.1036585000783</v>
+        <v>452.8460427179565</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>90.49711257789424</v>
+        <v>157.361466727191</v>
       </c>
       <c r="H12" t="n">
-        <v>229.9735274098612</v>
+        <v>187.3581448081296</v>
       </c>
       <c r="I12" t="n">
-        <v>279.2062147166107</v>
+        <v>294.438387671837</v>
       </c>
       <c r="J12" t="n">
-        <v>337.2787245425917</v>
+        <v>219.0052955025046</v>
       </c>
       <c r="K12" t="n">
-        <v>173.3836478329517</v>
+        <v>421.6591003189133</v>
       </c>
       <c r="L12" t="n">
-        <v>183.1392334432057</v>
+        <v>223.6863834221978</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>90.49711257789424</v>
+        <v>157.361466727191</v>
       </c>
       <c r="H13" t="n">
-        <v>229.9735274098612</v>
+        <v>187.3581448081296</v>
       </c>
       <c r="I13" t="n">
-        <v>279.2062147166107</v>
+        <v>294.438387671837</v>
       </c>
       <c r="J13" t="n">
-        <v>337.2787245425917</v>
+        <v>219.0052955025046</v>
       </c>
       <c r="K13" t="n">
-        <v>173.3836478329517</v>
+        <v>421.6591003189133</v>
       </c>
       <c r="L13" t="n">
-        <v>183.1392334432057</v>
+        <v>223.6863834221978</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.79424310448062e-15</v>
+        <v>3.896714452764359e-16</v>
       </c>
       <c r="B15" t="n">
-        <v>31.00848975065441</v>
+        <v>7.267258419981797</v>
       </c>
       <c r="C15" t="n">
-        <v>16.27205235351061</v>
+        <v>2.172317485627652</v>
       </c>
       <c r="D15" t="n">
-        <v>4.633438747396424</v>
+        <v>0.2031218468440417</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3845763708362961</v>
+        <v>0.007828880082645486</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.896714452764359e-16</v>
+        <v>4.369232328535308e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>2.737554051798655</v>
+        <v>3.509234304586537</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06986409927382436</v>
+        <v>0.02231472310047833</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1602253121937256</v>
+        <v>0.1984988493830444</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.002757997913445265</v>
+        <v>-0.005847353973372365</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1624692475139</v>
+        <v>262.9309215257846</v>
       </c>
       <c r="H2" t="n">
-        <v>106.101773727676</v>
+        <v>250.593119041376</v>
       </c>
       <c r="I2" t="n">
-        <v>277.4607960838766</v>
+        <v>189.3466472338478</v>
       </c>
       <c r="J2" t="n">
-        <v>183.5356138239177</v>
+        <v>170.5234795881971</v>
       </c>
       <c r="K2" t="n">
-        <v>300.2555102547457</v>
+        <v>435.2884958741394</v>
       </c>
       <c r="L2" t="n">
-        <v>418.9762708994894</v>
+        <v>323.3535709215215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-3.295355185473915e-16</v>
+        <v>-3.443652091672978e-16</v>
       </c>
       <c r="B3" t="n">
-        <v>5.497067341572366</v>
+        <v>4.348314216995742</v>
       </c>
       <c r="C3" t="n">
-        <v>0.932378557680911</v>
+        <v>0.7781640155346254</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07674321454966482</v>
+        <v>0.05325486836358036</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002251653634490288</v>
+        <v>-0.00208930724173994</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>222.8439743021924</v>
+        <v>161.0139463959628</v>
       </c>
       <c r="H3" t="n">
-        <v>226.1076609327292</v>
+        <v>114.3257286655506</v>
       </c>
       <c r="I3" t="n">
-        <v>159.6676690574295</v>
+        <v>237.6764467918796</v>
       </c>
       <c r="J3" t="n">
-        <v>359.6462063428085</v>
+        <v>157.9701713751696</v>
       </c>
       <c r="K3" t="n">
-        <v>241.6602823736781</v>
+        <v>338.1126726778903</v>
       </c>
       <c r="L3" t="n">
-        <v>261.1978359276691</v>
+        <v>171.6279553071195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9.020282803053189e-19</v>
+        <v>-1.096151676971938e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>7.267258419981797</v>
+        <v>7.275507434887453</v>
       </c>
       <c r="C4" t="n">
-        <v>2.158576295222186</v>
+        <v>2.15875806407584</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1957796907205593</v>
+        <v>0.1948114251957908</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007255518498455599</v>
+        <v>0.006270868856277663</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>95.14499516009055</v>
+        <v>139.8692027260821</v>
       </c>
       <c r="H4" t="n">
-        <v>233.9689608005009</v>
+        <v>198.4484203120851</v>
       </c>
       <c r="I4" t="n">
-        <v>331.8563576416215</v>
+        <v>252.7341466287384</v>
       </c>
       <c r="J4" t="n">
-        <v>182.7442176710605</v>
+        <v>250.5544342742573</v>
       </c>
       <c r="K4" t="n">
-        <v>312.7598149390951</v>
+        <v>164.2193349486311</v>
       </c>
       <c r="L4" t="n">
-        <v>289.7143745797266</v>
+        <v>377.3897286667829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-6.117474266014258e-17</v>
+        <v>-6.690592849368672e-17</v>
       </c>
       <c r="B5" t="n">
-        <v>-3.633766504446859</v>
+        <v>-3.660079684364874</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.131500906967353</v>
+        <v>-2.119240722136432</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1688118667512442</v>
+        <v>-0.1968574971237458</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002156390022992584</v>
+        <v>0.004080059420644054</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>217.6336834131148</v>
+        <v>191.303160841143</v>
       </c>
       <c r="H5" t="n">
-        <v>224.5306576761033</v>
+        <v>180.5865156123098</v>
       </c>
       <c r="I5" t="n">
-        <v>261.6447977818998</v>
+        <v>267.3196705950712</v>
       </c>
       <c r="J5" t="n">
-        <v>292.1049828638553</v>
+        <v>147.629463253428</v>
       </c>
       <c r="K5" t="n">
-        <v>241.779662896094</v>
+        <v>438.9592208262376</v>
       </c>
       <c r="L5" t="n">
-        <v>355.1180756334485</v>
+        <v>345.842845662039</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.055930742908061e-17</v>
+        <v>-6.541125813622848e-17</v>
       </c>
       <c r="B6" t="n">
-        <v>6.173514705675393</v>
+        <v>6.184280267216384</v>
       </c>
       <c r="C6" t="n">
-        <v>2.172317485627652</v>
+        <v>2.172360304770735</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2027027241466817</v>
+        <v>0.202888306899548</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006636470843877285</v>
+        <v>0.006842554569799453</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>153.6074935304167</v>
+        <v>151.0384155741571</v>
       </c>
       <c r="H6" t="n">
-        <v>226.9016543952538</v>
+        <v>232.7419621731932</v>
       </c>
       <c r="I6" t="n">
-        <v>336.470339540183</v>
+        <v>257.6114779613218</v>
       </c>
       <c r="J6" t="n">
-        <v>258.0140376927241</v>
+        <v>169.5852684107635</v>
       </c>
       <c r="K6" t="n">
-        <v>470.5521282863169</v>
+        <v>268.1783266636024</v>
       </c>
       <c r="L6" t="n">
-        <v>405.6950453514312</v>
+        <v>262.4387458311487</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.255896232806766e-17</v>
+        <v>1.119443035298385e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2051034198074366</v>
+        <v>0.9216233176434487</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.172544866685358</v>
+        <v>-2.172328915215547</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2029742037666173</v>
+        <v>-0.202824541857372</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007344350569165229</v>
+        <v>-0.003518574508551281</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>91.32774854755333</v>
+        <v>210.3202613961717</v>
       </c>
       <c r="H7" t="n">
-        <v>167.0767432473507</v>
+        <v>160.5938251362804</v>
       </c>
       <c r="I7" t="n">
-        <v>326.7948502760407</v>
+        <v>322.8635502028208</v>
       </c>
       <c r="J7" t="n">
-        <v>334.3775397079096</v>
+        <v>254.192471832567</v>
       </c>
       <c r="K7" t="n">
-        <v>425.8000464268531</v>
+        <v>221.3177177024994</v>
       </c>
       <c r="L7" t="n">
-        <v>354.9993669547285</v>
+        <v>285.4775941173374</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.085217845472576e-16</v>
+        <v>1.141851182777251e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>4.800307518608793</v>
+        <v>3.677916292224647</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1355644008929682</v>
+        <v>-0.1405338142185297</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2031218468440417</v>
+        <v>0.2031216667433313</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0003151999537749535</v>
+        <v>0.0007774498665639034</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>130.4123435782047</v>
+        <v>90.79656676981155</v>
       </c>
       <c r="H8" t="n">
-        <v>221.7717244399619</v>
+        <v>234.1307011604318</v>
       </c>
       <c r="I8" t="n">
-        <v>213.1724318371147</v>
+        <v>191.9633015571191</v>
       </c>
       <c r="J8" t="n">
-        <v>234.7475776197601</v>
+        <v>278.0272657358925</v>
       </c>
       <c r="K8" t="n">
-        <v>169.2539968887581</v>
+        <v>208.6030515822439</v>
       </c>
       <c r="L8" t="n">
-        <v>210.4631843872227</v>
+        <v>296.5229552581735</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-3.072499163359244e-18</v>
+        <v>3.782068713035025e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.9567436167784098</v>
+        <v>5.150488181673553</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.945344244893715</v>
+        <v>0.04408566339922632</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2031216631868815</v>
+        <v>-0.2031246564133402</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0007951444826114006</v>
+        <v>0.0007486420864025826</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>113.7575893067084</v>
+        <v>133.6862570489017</v>
       </c>
       <c r="H9" t="n">
-        <v>244.987381535725</v>
+        <v>158.3116013939234</v>
       </c>
       <c r="I9" t="n">
-        <v>341.588748707119</v>
+        <v>164.5697315079758</v>
       </c>
       <c r="J9" t="n">
-        <v>289.3378789733964</v>
+        <v>149.9922340813116</v>
       </c>
       <c r="K9" t="n">
-        <v>201.5798243302697</v>
+        <v>276.445576150904</v>
       </c>
       <c r="L9" t="n">
-        <v>202.5173681864425</v>
+        <v>270.1608059793848</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.518219360788948e-17</v>
+        <v>-7.520838023623159e-18</v>
       </c>
       <c r="B10" t="n">
-        <v>2.967641730304288</v>
+        <v>3.616759721407124</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.097286627394027</v>
+        <v>-1.220394042897019</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2029266557956295</v>
+        <v>-0.2029379341052776</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007828880082645486</v>
+        <v>0.0078302274230879</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>132.8769030567743</v>
+        <v>262.1238657839883</v>
       </c>
       <c r="H10" t="n">
-        <v>258.6872592810095</v>
+        <v>260.7838098832204</v>
       </c>
       <c r="I10" t="n">
-        <v>139.1130445947136</v>
+        <v>265.3483843434504</v>
       </c>
       <c r="J10" t="n">
-        <v>292.157659285013</v>
+        <v>309.1625476027825</v>
       </c>
       <c r="K10" t="n">
-        <v>448.0945606398641</v>
+        <v>356.5473552379969</v>
       </c>
       <c r="L10" t="n">
-        <v>274.0920069477049</v>
+        <v>183.6233003785019</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.568269645545887e-17</v>
+        <v>1.481746108223539e-16</v>
       </c>
       <c r="B11" t="n">
-        <v>5.695513254692193</v>
+        <v>4.23300683046463</v>
       </c>
       <c r="C11" t="n">
-        <v>1.434949470147667</v>
+        <v>-0.8185232967918817</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2029583521528772</v>
+        <v>0.2029508253962183</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007830636951523761</v>
+        <v>-0.00783071971882288</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>209.616503710768</v>
+        <v>229.9114995385827</v>
       </c>
       <c r="H11" t="n">
-        <v>126.9719853100555</v>
+        <v>102.4426541791653</v>
       </c>
       <c r="I11" t="n">
-        <v>263.0752389717435</v>
+        <v>242.2950504597384</v>
       </c>
       <c r="J11" t="n">
-        <v>211.0447222529531</v>
+        <v>357.8141211899173</v>
       </c>
       <c r="K11" t="n">
-        <v>430.4404075677971</v>
+        <v>371.2053684897553</v>
       </c>
       <c r="L11" t="n">
-        <v>452.8460427179565</v>
+        <v>166.6124319102381</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>157.361466727191</v>
+        <v>92.37909454555187</v>
       </c>
       <c r="H12" t="n">
-        <v>187.3581448081296</v>
+        <v>233.2307720590494</v>
       </c>
       <c r="I12" t="n">
-        <v>294.438387671837</v>
+        <v>121.8987392643202</v>
       </c>
       <c r="J12" t="n">
-        <v>219.0052955025046</v>
+        <v>244.8174478316882</v>
       </c>
       <c r="K12" t="n">
-        <v>421.6591003189133</v>
+        <v>222.3005622628649</v>
       </c>
       <c r="L12" t="n">
-        <v>223.6863834221978</v>
+        <v>319.2995454049861</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>157.361466727191</v>
+        <v>92.37909454555187</v>
       </c>
       <c r="H13" t="n">
-        <v>187.3581448081296</v>
+        <v>233.2307720590494</v>
       </c>
       <c r="I13" t="n">
-        <v>294.438387671837</v>
+        <v>121.8987392643202</v>
       </c>
       <c r="J13" t="n">
-        <v>219.0052955025046</v>
+        <v>244.8174478316882</v>
       </c>
       <c r="K13" t="n">
-        <v>421.6591003189133</v>
+        <v>222.3005622628649</v>
       </c>
       <c r="L13" t="n">
-        <v>223.6863834221978</v>
+        <v>319.2995454049861</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.896714452764359e-16</v>
+        <v>4.369232328535308e-16</v>
       </c>
       <c r="B15" t="n">
-        <v>7.267258419981797</v>
+        <v>7.275507434887453</v>
       </c>
       <c r="C15" t="n">
-        <v>2.172317485627652</v>
+        <v>2.172360304770735</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2031218468440417</v>
+        <v>0.2031216667433313</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007828880082645486</v>
+        <v>0.0078302274230879</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.369232328535308e-16</v>
+        <v>4.691782867654174e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>3.509234304586537</v>
+        <v>8.568828798017265</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02231472310047833</v>
+        <v>1.616416139369957</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1984988493830444</v>
+        <v>-0.1421025188292863</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.005847353973372365</v>
+        <v>-0.004328396022916045</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>262.9309215257846</v>
+        <v>215.0726248022922</v>
       </c>
       <c r="H2" t="n">
-        <v>250.593119041376</v>
+        <v>207.9346329650483</v>
       </c>
       <c r="I2" t="n">
-        <v>189.3466472338478</v>
+        <v>169.9171209843221</v>
       </c>
       <c r="J2" t="n">
-        <v>170.5234795881971</v>
+        <v>213.2018219615335</v>
       </c>
       <c r="K2" t="n">
-        <v>435.2884958741394</v>
+        <v>193.7513158153378</v>
       </c>
       <c r="L2" t="n">
-        <v>323.3535709215215</v>
+        <v>185.0806846688032</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-3.443652091672978e-16</v>
+        <v>-4.450914406332993e-16</v>
       </c>
       <c r="B3" t="n">
-        <v>4.348314216995742</v>
+        <v>12.22227194583463</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7781640155346254</v>
+        <v>0.9591828464969584</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05325486836358036</v>
+        <v>0.194875136789229</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.00208930724173994</v>
+        <v>-0.005861963408374389</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>161.0139463959628</v>
+        <v>196.7744509358578</v>
       </c>
       <c r="H3" t="n">
-        <v>114.3257286655506</v>
+        <v>239.9901963770123</v>
       </c>
       <c r="I3" t="n">
-        <v>237.6764467918796</v>
+        <v>306.3384403869329</v>
       </c>
       <c r="J3" t="n">
-        <v>157.9701713751696</v>
+        <v>333.6972478704073</v>
       </c>
       <c r="K3" t="n">
-        <v>338.1126726778903</v>
+        <v>276.518533793306</v>
       </c>
       <c r="L3" t="n">
-        <v>171.6279553071195</v>
+        <v>267.520237700501</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.096151676971938e-16</v>
+        <v>1.122363523840749e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>7.275507434887453</v>
+        <v>14.52488130032127</v>
       </c>
       <c r="C4" t="n">
-        <v>2.15875806407584</v>
+        <v>3.247643124697207</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1948114251957908</v>
+        <v>0.1876757544393909</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006270868856277663</v>
+        <v>-0.005213900617646638</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>139.8692027260821</v>
+        <v>131.2786099384052</v>
       </c>
       <c r="H4" t="n">
-        <v>198.4484203120851</v>
+        <v>250.0317385949927</v>
       </c>
       <c r="I4" t="n">
-        <v>252.7341466287384</v>
+        <v>244.3897665999187</v>
       </c>
       <c r="J4" t="n">
-        <v>250.5544342742573</v>
+        <v>165.0389639245632</v>
       </c>
       <c r="K4" t="n">
-        <v>164.2193349486311</v>
+        <v>419.0759890310393</v>
       </c>
       <c r="L4" t="n">
-        <v>377.3897286667829</v>
+        <v>207.6443914820977</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-6.690592849368672e-17</v>
+        <v>4.721721347937581e-17</v>
       </c>
       <c r="B5" t="n">
-        <v>-3.660079684364874</v>
+        <v>-6.693887947543552</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.119240722136432</v>
+        <v>-3.212805837060288</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1968574971237458</v>
+        <v>-0.1971534819961066</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004080059420644054</v>
+        <v>-0.007561199417942482</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>191.303160841143</v>
+        <v>99.42227809818651</v>
       </c>
       <c r="H5" t="n">
-        <v>180.5865156123098</v>
+        <v>195.9041078689584</v>
       </c>
       <c r="I5" t="n">
-        <v>267.3196705950712</v>
+        <v>174.2928910695422</v>
       </c>
       <c r="J5" t="n">
-        <v>147.629463253428</v>
+        <v>174.6185384676436</v>
       </c>
       <c r="K5" t="n">
-        <v>438.9592208262376</v>
+        <v>347.0606765947147</v>
       </c>
       <c r="L5" t="n">
-        <v>345.842845662039</v>
+        <v>293.9047343562585</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-6.541125813622848e-17</v>
+        <v>1.108359113476444e-16</v>
       </c>
       <c r="B6" t="n">
-        <v>6.184280267216384</v>
+        <v>8.609332028616155</v>
       </c>
       <c r="C6" t="n">
-        <v>2.172360304770735</v>
+        <v>3.271628708323247</v>
       </c>
       <c r="D6" t="n">
-        <v>0.202888306899548</v>
+        <v>0.2029811892417671</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006842554569799453</v>
+        <v>-0.005470099100115373</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>151.0384155741571</v>
+        <v>206.2356115480653</v>
       </c>
       <c r="H6" t="n">
-        <v>232.7419621731932</v>
+        <v>163.1217528687789</v>
       </c>
       <c r="I6" t="n">
-        <v>257.6114779613218</v>
+        <v>217.7026266429486</v>
       </c>
       <c r="J6" t="n">
-        <v>169.5852684107635</v>
+        <v>333.9796511443623</v>
       </c>
       <c r="K6" t="n">
-        <v>268.1783266636024</v>
+        <v>439.9903235221292</v>
       </c>
       <c r="L6" t="n">
-        <v>262.4387458311487</v>
+        <v>364.8366764151382</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.119443035298385e-16</v>
+        <v>-7.619972966221606e-17</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9216233176434487</v>
+        <v>7.821222951528544</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.172328915215547</v>
+        <v>-3.272803933977945</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.202824541857372</v>
+        <v>-0.2030562642183016</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.003518574508551281</v>
+        <v>0.003066269570319326</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>210.3202613961717</v>
+        <v>90.10220990597134</v>
       </c>
       <c r="H7" t="n">
-        <v>160.5938251362804</v>
+        <v>175.4012366729903</v>
       </c>
       <c r="I7" t="n">
-        <v>322.8635502028208</v>
+        <v>247.5442017662156</v>
       </c>
       <c r="J7" t="n">
-        <v>254.192471832567</v>
+        <v>247.3207607780483</v>
       </c>
       <c r="K7" t="n">
-        <v>221.3177177024994</v>
+        <v>258.3020309745055</v>
       </c>
       <c r="L7" t="n">
-        <v>285.4775941173374</v>
+        <v>319.1957959478577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.141851182777251e-16</v>
+        <v>1.444710257344163e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>3.677916292224647</v>
+        <v>13.23818167121957</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1405338142185297</v>
+        <v>3.168248782096023</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2031216667433313</v>
+        <v>0.2031215892242177</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007774498665639034</v>
+        <v>0.0007705572033509834</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>90.79656676981155</v>
+        <v>261.4556162229031</v>
       </c>
       <c r="H8" t="n">
-        <v>234.1307011604318</v>
+        <v>129.501214935772</v>
       </c>
       <c r="I8" t="n">
-        <v>191.9633015571191</v>
+        <v>197.0030793097069</v>
       </c>
       <c r="J8" t="n">
-        <v>278.0272657358925</v>
+        <v>170.8877595913928</v>
       </c>
       <c r="K8" t="n">
-        <v>208.6030515822439</v>
+        <v>322.9484908073283</v>
       </c>
       <c r="L8" t="n">
-        <v>296.5229552581735</v>
+        <v>203.6389310009046</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.782068713035025e-17</v>
+        <v>-5.207520243766e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>5.150488181673553</v>
+        <v>7.308640482386348</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04408566339922632</v>
+        <v>-1.890713208275677</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2031246564133402</v>
+        <v>-0.2031255278670108</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0007486420864025826</v>
+        <v>-0.0002886131224947452</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>133.6862570489017</v>
+        <v>151.3455260350566</v>
       </c>
       <c r="H9" t="n">
-        <v>158.3116013939234</v>
+        <v>169.9392146678988</v>
       </c>
       <c r="I9" t="n">
-        <v>164.5697315079758</v>
+        <v>242.5740183442258</v>
       </c>
       <c r="J9" t="n">
-        <v>149.9922340813116</v>
+        <v>218.2885218675283</v>
       </c>
       <c r="K9" t="n">
-        <v>276.445576150904</v>
+        <v>392.5067068395122</v>
       </c>
       <c r="L9" t="n">
-        <v>270.1608059793848</v>
+        <v>230.2287898764592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-7.520838023623159e-18</v>
+        <v>-1.328197186547799e-17</v>
       </c>
       <c r="B10" t="n">
-        <v>3.616759721407124</v>
+        <v>5.222484323557057</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.220394042897019</v>
+        <v>0.16341457459317</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2029379341052776</v>
+        <v>-0.2029586363114567</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0078302274230879</v>
+        <v>0.007830578738937497</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>262.1238657839883</v>
+        <v>138.5366066680242</v>
       </c>
       <c r="H10" t="n">
-        <v>260.7838098832204</v>
+        <v>184.9247285901325</v>
       </c>
       <c r="I10" t="n">
-        <v>265.3483843434504</v>
+        <v>162.9318341934817</v>
       </c>
       <c r="J10" t="n">
-        <v>309.1625476027825</v>
+        <v>331.0159851404583</v>
       </c>
       <c r="K10" t="n">
-        <v>356.5473552379969</v>
+        <v>213.2772426807919</v>
       </c>
       <c r="L10" t="n">
-        <v>183.6233003785019</v>
+        <v>202.1940897674032</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.481746108223539e-16</v>
+        <v>3.312986342686658e-17</v>
       </c>
       <c r="B11" t="n">
-        <v>4.23300683046463</v>
+        <v>-6.626484897976594</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.8185232967918817</v>
+        <v>-3.271638413694874</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2029508253962183</v>
+        <v>-0.2029555104888276</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.00783071971882288</v>
+        <v>-0.007830837554917902</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>229.9114995385827</v>
+        <v>222.9971680034504</v>
       </c>
       <c r="H11" t="n">
-        <v>102.4426541791653</v>
+        <v>99.66364827678171</v>
       </c>
       <c r="I11" t="n">
-        <v>242.2950504597384</v>
+        <v>275.51551458747</v>
       </c>
       <c r="J11" t="n">
-        <v>357.8141211899173</v>
+        <v>144.309693780466</v>
       </c>
       <c r="K11" t="n">
-        <v>371.2053684897553</v>
+        <v>186.9632134486625</v>
       </c>
       <c r="L11" t="n">
-        <v>166.6124319102381</v>
+        <v>414.3098471159769</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>92.37909454555187</v>
+        <v>204.4582406589592</v>
       </c>
       <c r="H12" t="n">
-        <v>233.2307720590494</v>
+        <v>230.5089505503077</v>
       </c>
       <c r="I12" t="n">
-        <v>121.8987392643202</v>
+        <v>246.8543434508836</v>
       </c>
       <c r="J12" t="n">
-        <v>244.8174478316882</v>
+        <v>252.5665560363857</v>
       </c>
       <c r="K12" t="n">
-        <v>222.3005622628649</v>
+        <v>275.8901355628469</v>
       </c>
       <c r="L12" t="n">
-        <v>319.2995454049861</v>
+        <v>214.1734481962645</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>92.37909454555187</v>
+        <v>204.4582406589592</v>
       </c>
       <c r="H13" t="n">
-        <v>233.2307720590494</v>
+        <v>230.5089505503077</v>
       </c>
       <c r="I13" t="n">
-        <v>121.8987392643202</v>
+        <v>246.8543434508836</v>
       </c>
       <c r="J13" t="n">
-        <v>244.8174478316882</v>
+        <v>252.5665560363857</v>
       </c>
       <c r="K13" t="n">
-        <v>222.3005622628649</v>
+        <v>275.8901355628469</v>
       </c>
       <c r="L13" t="n">
-        <v>319.2995454049861</v>
+        <v>214.1734481962645</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.369232328535308e-16</v>
+        <v>4.691782867654174e-16</v>
       </c>
       <c r="B15" t="n">
-        <v>7.275507434887453</v>
+        <v>14.52488130032127</v>
       </c>
       <c r="C15" t="n">
-        <v>2.172360304770735</v>
+        <v>3.271628708323247</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2031216667433313</v>
+        <v>0.2031215892242177</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0078302274230879</v>
+        <v>0.007830578738937497</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.691782867654174e-16</v>
+        <v>4.063524445482365e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>8.568828798017265</v>
+        <v>3.916541341086006</v>
       </c>
       <c r="C2" t="n">
-        <v>1.616416139369957</v>
+        <v>1.906077320652793</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1421025188292863</v>
+        <v>0.2028584521640072</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004328396022916045</v>
+        <v>0.004925361909771284</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>215.0726248022922</v>
+        <v>-208.1745872777258</v>
       </c>
       <c r="H2" t="n">
-        <v>207.9346329650483</v>
+        <v>-203.0419183346576</v>
       </c>
       <c r="I2" t="n">
-        <v>169.9171209843221</v>
+        <v>-246.1550574309999</v>
       </c>
       <c r="J2" t="n">
-        <v>213.2018219615335</v>
+        <v>-146.6725370012521</v>
       </c>
       <c r="K2" t="n">
-        <v>193.7513158153378</v>
+        <v>-141.1177935318975</v>
       </c>
       <c r="L2" t="n">
-        <v>185.0806846688032</v>
+        <v>-279.9129905442529</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-4.450914406332993e-16</v>
+        <v>-3.368415777166166e-16</v>
       </c>
       <c r="B3" t="n">
-        <v>12.22227194583463</v>
+        <v>4.471184443022047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9591828464969584</v>
+        <v>0.1453697554498275</v>
       </c>
       <c r="D3" t="n">
-        <v>0.194875136789229</v>
+        <v>0.04873379862579773</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.005861963408374389</v>
+        <v>0.001273478104138466</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>196.7744509358578</v>
+        <v>-293.2294369792257</v>
       </c>
       <c r="H3" t="n">
-        <v>239.9901963770123</v>
+        <v>-120.0686845491362</v>
       </c>
       <c r="I3" t="n">
-        <v>306.3384403869329</v>
+        <v>-184.6342420815687</v>
       </c>
       <c r="J3" t="n">
-        <v>333.6972478704073</v>
+        <v>-147.6193050711527</v>
       </c>
       <c r="K3" t="n">
-        <v>276.518533793306</v>
+        <v>-105.8567527211622</v>
       </c>
       <c r="L3" t="n">
-        <v>267.520237700501</v>
+        <v>-144.6282402760124</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.122363523840749e-16</v>
+        <v>1.704925907841156e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>14.52488130032127</v>
+        <v>6.637260372540447</v>
       </c>
       <c r="C4" t="n">
-        <v>3.247643124697207</v>
+        <v>1.638484214475896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1876757544393909</v>
+        <v>0.2030538491808176</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005213900617646638</v>
+        <v>0.003529031722155214</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>131.2786099384052</v>
+        <v>-231.4652342148976</v>
       </c>
       <c r="H4" t="n">
-        <v>250.0317385949927</v>
+        <v>-144.9260177355144</v>
       </c>
       <c r="I4" t="n">
-        <v>244.3897665999187</v>
+        <v>-109.371194272712</v>
       </c>
       <c r="J4" t="n">
-        <v>165.0389639245632</v>
+        <v>-209.6727899851831</v>
       </c>
       <c r="K4" t="n">
-        <v>419.0759890310393</v>
+        <v>-287.0280676770373</v>
       </c>
       <c r="L4" t="n">
-        <v>207.6443914820977</v>
+        <v>-115.5911673879991</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.721721347937581e-17</v>
+        <v>9.671613097345813e-17</v>
       </c>
       <c r="B5" t="n">
-        <v>-6.693887947543552</v>
+        <v>-4.766466998461144</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.212805837060288</v>
+        <v>-1.006881167702509</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1971534819961066</v>
+        <v>-0.1189107041234773</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.007561199417942482</v>
+        <v>-0.001890699315824726</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>99.42227809818651</v>
+        <v>-231.3221909900807</v>
       </c>
       <c r="H5" t="n">
-        <v>195.9041078689584</v>
+        <v>-123.9776782299967</v>
       </c>
       <c r="I5" t="n">
-        <v>174.2928910695422</v>
+        <v>-295.4473707277004</v>
       </c>
       <c r="J5" t="n">
-        <v>174.6185384676436</v>
+        <v>-143.2152345712038</v>
       </c>
       <c r="K5" t="n">
-        <v>347.0606765947147</v>
+        <v>-179.8649574859882</v>
       </c>
       <c r="L5" t="n">
-        <v>293.9047343562585</v>
+        <v>-259.3292697400526</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.108359113476444e-16</v>
+        <v>5.144069548575249e-17</v>
       </c>
       <c r="B6" t="n">
-        <v>8.609332028616155</v>
+        <v>-0.5197585358209855</v>
       </c>
       <c r="C6" t="n">
-        <v>3.271628708323247</v>
+        <v>2.17264233183042</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2029811892417671</v>
+        <v>0.2030268927719243</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005470099100115373</v>
+        <v>0.004156656352952934</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>206.2356115480653</v>
+        <v>-272.4871604646153</v>
       </c>
       <c r="H6" t="n">
-        <v>163.1217528687789</v>
+        <v>-280.9303057016181</v>
       </c>
       <c r="I6" t="n">
-        <v>217.7026266429486</v>
+        <v>-276.4034253494459</v>
       </c>
       <c r="J6" t="n">
-        <v>333.9796511443623</v>
+        <v>-104.6192128118125</v>
       </c>
       <c r="K6" t="n">
-        <v>439.9903235221292</v>
+        <v>-179.6040244803747</v>
       </c>
       <c r="L6" t="n">
-        <v>364.8366764151382</v>
+        <v>-269.5248598955652</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-7.619972966221606e-17</v>
+        <v>-4.303938579808872e-17</v>
       </c>
       <c r="B7" t="n">
-        <v>7.821222951528544</v>
+        <v>2.923377079033285</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.272803933977945</v>
+        <v>-2.172596314265808</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2030562642183016</v>
+        <v>-0.2030119275769316</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003066269570319326</v>
+        <v>-0.005451478560159417</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>90.10220990597134</v>
+        <v>-151.1712455560321</v>
       </c>
       <c r="H7" t="n">
-        <v>175.4012366729903</v>
+        <v>-271.6705838337439</v>
       </c>
       <c r="I7" t="n">
-        <v>247.5442017662156</v>
+        <v>-256.7060963646106</v>
       </c>
       <c r="J7" t="n">
-        <v>247.3207607780483</v>
+        <v>-142.1653804239488</v>
       </c>
       <c r="K7" t="n">
-        <v>258.3020309745055</v>
+        <v>-279.0205017488011</v>
       </c>
       <c r="L7" t="n">
-        <v>319.1957959478577</v>
+        <v>-185.061471328837</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.444710257344163e-16</v>
+        <v>7.833661742275462e-17</v>
       </c>
       <c r="B8" t="n">
-        <v>13.23818167121957</v>
+        <v>-1.440363643336592</v>
       </c>
       <c r="C8" t="n">
-        <v>3.168248782096023</v>
+        <v>2.152773694730953</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2031215892242177</v>
+        <v>0.2031247678598138</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007705572033509834</v>
+        <v>-0.0002946371425437736</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>261.4556162229031</v>
+        <v>-183.8988453315329</v>
       </c>
       <c r="H8" t="n">
-        <v>129.501214935772</v>
+        <v>-280.9776195213938</v>
       </c>
       <c r="I8" t="n">
-        <v>197.0030793097069</v>
+        <v>-103.5165858071256</v>
       </c>
       <c r="J8" t="n">
-        <v>170.8877595913928</v>
+        <v>-194.5448059550203</v>
       </c>
       <c r="K8" t="n">
-        <v>322.9484908073283</v>
+        <v>-224.658804549328</v>
       </c>
       <c r="L8" t="n">
-        <v>203.6389310009046</v>
+        <v>-118.760409201183</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-5.207520243766e-17</v>
+        <v>6.504622165983421e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>7.308640482386348</v>
+        <v>2.875417210005948</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.890713208275677</v>
+        <v>-2.002641016924062</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2031255278670108</v>
+        <v>-0.203123901232551</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0002886131224947452</v>
+        <v>0.000937797406897592</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>151.3455260350566</v>
+        <v>-140.8275831216113</v>
       </c>
       <c r="H9" t="n">
-        <v>169.9392146678988</v>
+        <v>-246.2728678862812</v>
       </c>
       <c r="I9" t="n">
-        <v>242.5740183442258</v>
+        <v>-196.5882572474681</v>
       </c>
       <c r="J9" t="n">
-        <v>218.2885218675283</v>
+        <v>-189.3672629472696</v>
       </c>
       <c r="K9" t="n">
-        <v>392.5067068395122</v>
+        <v>-220.0206695226231</v>
       </c>
       <c r="L9" t="n">
-        <v>230.2287898764592</v>
+        <v>-133.861951162339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1.328197186547799e-17</v>
+        <v>-1.863651697540624e-16</v>
       </c>
       <c r="B10" t="n">
-        <v>5.222484323557057</v>
+        <v>0.5826893957639101</v>
       </c>
       <c r="C10" t="n">
-        <v>0.16341457459317</v>
+        <v>-1.673756150158109</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2029586363114567</v>
+        <v>0.2029583035456022</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007830578738937497</v>
+        <v>0.007829986794926467</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>138.5366066680242</v>
+        <v>-154.39409998759</v>
       </c>
       <c r="H10" t="n">
-        <v>184.9247285901325</v>
+        <v>-262.8754186897602</v>
       </c>
       <c r="I10" t="n">
-        <v>162.9318341934817</v>
+        <v>-182.7291684390804</v>
       </c>
       <c r="J10" t="n">
-        <v>331.0159851404583</v>
+        <v>-210.2113947718159</v>
       </c>
       <c r="K10" t="n">
-        <v>213.2772426807919</v>
+        <v>-269.209651321293</v>
       </c>
       <c r="L10" t="n">
-        <v>202.1940897674032</v>
+        <v>-298.6447000845739</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.312986342686658e-17</v>
+        <v>-3.306700140884343e-17</v>
       </c>
       <c r="B11" t="n">
-        <v>-6.626484897976594</v>
+        <v>0.366540782828827</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.271638413694874</v>
+        <v>1.476312830276173</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2029555104888276</v>
+        <v>-0.2028757409776071</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007830837554917902</v>
+        <v>-0.007823538990350171</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>222.9971680034504</v>
+        <v>-281.3685620372889</v>
       </c>
       <c r="H11" t="n">
-        <v>99.66364827678171</v>
+        <v>-280.4087536240257</v>
       </c>
       <c r="I11" t="n">
-        <v>275.51551458747</v>
+        <v>-282.6744295386466</v>
       </c>
       <c r="J11" t="n">
-        <v>144.309693780466</v>
+        <v>-220.6441498996765</v>
       </c>
       <c r="K11" t="n">
-        <v>186.9632134486625</v>
+        <v>-236.6576908197543</v>
       </c>
       <c r="L11" t="n">
-        <v>414.3098471159769</v>
+        <v>-206.0416915890776</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>204.4582406589592</v>
+        <v>-172.7103297485407</v>
       </c>
       <c r="H12" t="n">
-        <v>230.5089505503077</v>
+        <v>-186.3159208167994</v>
       </c>
       <c r="I12" t="n">
-        <v>246.8543434508836</v>
+        <v>-110.1601648855138</v>
       </c>
       <c r="J12" t="n">
-        <v>252.5665560363857</v>
+        <v>-275.0342298516327</v>
       </c>
       <c r="K12" t="n">
-        <v>275.8901355628469</v>
+        <v>-189.4738739884041</v>
       </c>
       <c r="L12" t="n">
-        <v>214.1734481962645</v>
+        <v>-249.3092308006451</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>204.4582406589592</v>
+        <v>-172.7103297485407</v>
       </c>
       <c r="H13" t="n">
-        <v>230.5089505503077</v>
+        <v>-186.3159208167994</v>
       </c>
       <c r="I13" t="n">
-        <v>246.8543434508836</v>
+        <v>-110.1601648855138</v>
       </c>
       <c r="J13" t="n">
-        <v>252.5665560363857</v>
+        <v>-275.0342298516327</v>
       </c>
       <c r="K13" t="n">
-        <v>275.8901355628469</v>
+        <v>-189.4738739884041</v>
       </c>
       <c r="L13" t="n">
-        <v>214.1734481962645</v>
+        <v>-249.3092308006451</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.691782867654174e-16</v>
+        <v>4.063524445482365e-16</v>
       </c>
       <c r="B15" t="n">
-        <v>14.52488130032127</v>
+        <v>6.637260372540447</v>
       </c>
       <c r="C15" t="n">
-        <v>3.271628708323247</v>
+        <v>2.17264233183042</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2031215892242177</v>
+        <v>0.2031247678598138</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007830578738937497</v>
+        <v>0.007829986794926467</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.063524445482365e-16</v>
+        <v>4.156315745383399e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>3.916541341086006</v>
+        <v>2.254949238885604</v>
       </c>
       <c r="C2" t="n">
-        <v>1.906077320652793</v>
+        <v>-1.059240274666308</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2028584521640072</v>
+        <v>0.08698347905029004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004925361909771284</v>
+        <v>-0.002243622526310631</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-208.1745872777258</v>
+        <v>-354.8169042986818</v>
       </c>
       <c r="H2" t="n">
-        <v>-203.0419183346576</v>
+        <v>-429.511816963417</v>
       </c>
       <c r="I2" t="n">
-        <v>-246.1550574309999</v>
+        <v>-269.5719452760135</v>
       </c>
       <c r="J2" t="n">
-        <v>-146.6725370012521</v>
+        <v>-505.7241886967951</v>
       </c>
       <c r="K2" t="n">
-        <v>-141.1177935318975</v>
+        <v>-437.9012958167249</v>
       </c>
       <c r="L2" t="n">
-        <v>-279.9129905442529</v>
+        <v>-428.810950591507</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-3.368415777166166e-16</v>
+        <v>-3.492241176509067e-16</v>
       </c>
       <c r="B3" t="n">
-        <v>4.471184443022047</v>
+        <v>1.095981578202815</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1453697554498275</v>
+        <v>2.01235715961866</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04873379862579773</v>
+        <v>0.09327117689595858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001273478104138466</v>
+        <v>0.0002610700426912064</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-293.2294369792257</v>
+        <v>-293.3306260360512</v>
       </c>
       <c r="H3" t="n">
-        <v>-120.0686845491362</v>
+        <v>-451.514793401242</v>
       </c>
       <c r="I3" t="n">
-        <v>-184.6342420815687</v>
+        <v>-527.6275370456608</v>
       </c>
       <c r="J3" t="n">
-        <v>-147.6193050711527</v>
+        <v>-205.3309720683288</v>
       </c>
       <c r="K3" t="n">
-        <v>-105.8567527211622</v>
+        <v>-214.2538267976783</v>
       </c>
       <c r="L3" t="n">
-        <v>-144.6282402760124</v>
+        <v>-292.5052561886603</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.704925907841156e-16</v>
+        <v>5.742098362495043e-17</v>
       </c>
       <c r="B4" t="n">
-        <v>6.637260372540447</v>
+        <v>7.28371711017866</v>
       </c>
       <c r="C4" t="n">
-        <v>1.638484214475896</v>
+        <v>2.165144638473163</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2030538491808176</v>
+        <v>0.1968891739082204</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003529031722155214</v>
+        <v>-0.007149811023201835</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-231.4652342148976</v>
+        <v>-307.1206925993739</v>
       </c>
       <c r="H4" t="n">
-        <v>-144.9260177355144</v>
+        <v>-290.4918092779238</v>
       </c>
       <c r="I4" t="n">
-        <v>-109.371194272712</v>
+        <v>-433.6065281525437</v>
       </c>
       <c r="J4" t="n">
-        <v>-209.6727899851831</v>
+        <v>-479.6953887603854</v>
       </c>
       <c r="K4" t="n">
-        <v>-287.0280676770373</v>
+        <v>-525.2257521762867</v>
       </c>
       <c r="L4" t="n">
-        <v>-115.5911673879991</v>
+        <v>-518.1799601044149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9.671613097345813e-17</v>
+        <v>-5.785026462574634e-17</v>
       </c>
       <c r="B5" t="n">
-        <v>-4.766466998461144</v>
+        <v>-7.290727800952435</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.006881167702509</v>
+        <v>-2.172375568286604</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1189107041234773</v>
+        <v>-0.2028678434365219</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001890699315824726</v>
+        <v>0.004332958634543515</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-231.3221909900807</v>
+        <v>-477.6089246965869</v>
       </c>
       <c r="H5" t="n">
-        <v>-123.9776782299967</v>
+        <v>-408.642784880463</v>
       </c>
       <c r="I5" t="n">
-        <v>-295.4473707277004</v>
+        <v>-265.5485707280959</v>
       </c>
       <c r="J5" t="n">
-        <v>-143.2152345712038</v>
+        <v>-365.0694964038881</v>
       </c>
       <c r="K5" t="n">
-        <v>-179.8649574859882</v>
+        <v>-216.125888468655</v>
       </c>
       <c r="L5" t="n">
-        <v>-259.3292697400526</v>
+        <v>-494.6412523822127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5.144069548575249e-17</v>
+        <v>-1.468809157357587e-16</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.5197585358209855</v>
+        <v>-1.492181493768099</v>
       </c>
       <c r="C6" t="n">
-        <v>2.17264233183042</v>
+        <v>2.172379884075227</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2030268927719243</v>
+        <v>0.2029709606888156</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004156656352952934</v>
+        <v>-0.007146405796164886</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-272.4871604646153</v>
+        <v>-303.7171302886558</v>
       </c>
       <c r="H6" t="n">
-        <v>-280.9303057016181</v>
+        <v>-478.7418864916751</v>
       </c>
       <c r="I6" t="n">
-        <v>-276.4034253494459</v>
+        <v>-211.4946424371041</v>
       </c>
       <c r="J6" t="n">
-        <v>-104.6192128118125</v>
+        <v>-398.6101779175913</v>
       </c>
       <c r="K6" t="n">
-        <v>-179.6040244803747</v>
+        <v>-484.0143052093359</v>
       </c>
       <c r="L6" t="n">
-        <v>-269.5248598955652</v>
+        <v>-342.2568006097193</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-4.303938579808872e-17</v>
+        <v>1.753489918413844e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>2.923377079033285</v>
+        <v>-0.7625972340132381</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.172596314265808</v>
+        <v>-2.172393901095227</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2030119275769316</v>
+        <v>-0.2028146438681043</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.005451478560159417</v>
+        <v>-0.005538069867868816</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-151.1712455560321</v>
+        <v>-191.6428436098091</v>
       </c>
       <c r="H7" t="n">
-        <v>-271.6705838337439</v>
+        <v>-336.643783728227</v>
       </c>
       <c r="I7" t="n">
-        <v>-256.7060963646106</v>
+        <v>-233.5503730979178</v>
       </c>
       <c r="J7" t="n">
-        <v>-142.1653804239488</v>
+        <v>-418.7777481352038</v>
       </c>
       <c r="K7" t="n">
-        <v>-279.0205017488011</v>
+        <v>-282.2524730034239</v>
       </c>
       <c r="L7" t="n">
-        <v>-185.061471328837</v>
+        <v>-347.713739820663</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7.833661742275462e-17</v>
+        <v>1.163612452399703e-17</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.440363643336592</v>
+        <v>-5.249363050429602</v>
       </c>
       <c r="C8" t="n">
-        <v>2.152773694730953</v>
+        <v>-0.3753966510173357</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2031247678598138</v>
+        <v>0.2031254353518038</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0002946371425437736</v>
+        <v>-6.580030949281934e-05</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-183.8988453315329</v>
+        <v>-178.9524807817842</v>
       </c>
       <c r="H8" t="n">
-        <v>-280.9776195213938</v>
+        <v>-248.9527637782896</v>
       </c>
       <c r="I8" t="n">
-        <v>-103.5165858071256</v>
+        <v>-400.0480728539233</v>
       </c>
       <c r="J8" t="n">
-        <v>-194.5448059550203</v>
+        <v>-207.0835056689129</v>
       </c>
       <c r="K8" t="n">
-        <v>-224.658804549328</v>
+        <v>-348.1094845946809</v>
       </c>
       <c r="L8" t="n">
-        <v>-118.760409201183</v>
+        <v>-446.4229447627749</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.504622165983421e-17</v>
+        <v>-9.222398353653273e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>2.875417210005948</v>
+        <v>-5.132395539356654</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.002641016924062</v>
+        <v>-0.3013650242668037</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.203123901232551</v>
+        <v>-0.2031238050562512</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000937797406897592</v>
+        <v>0.0009593615416338149</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-140.8275831216113</v>
+        <v>-413.1892393297293</v>
       </c>
       <c r="H9" t="n">
-        <v>-246.2728678862812</v>
+        <v>-289.9317293084947</v>
       </c>
       <c r="I9" t="n">
-        <v>-196.5882572474681</v>
+        <v>-425.8009448246612</v>
       </c>
       <c r="J9" t="n">
-        <v>-189.3672629472696</v>
+        <v>-378.014728484413</v>
       </c>
       <c r="K9" t="n">
-        <v>-220.0206695226231</v>
+        <v>-221.0862106343696</v>
       </c>
       <c r="L9" t="n">
-        <v>-133.861951162339</v>
+        <v>-486.6983157389856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1.863651697540624e-16</v>
+        <v>-4.319810308768216e-17</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5826893957639101</v>
+        <v>-3.425176253716237</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.673756150158109</v>
+        <v>0.4810725166299394</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2029583035456022</v>
+        <v>-0.2029457651895129</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007829986794926467</v>
+        <v>0.007830413205614567</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-154.39409998759</v>
+        <v>-204.0080771870923</v>
       </c>
       <c r="H10" t="n">
-        <v>-262.8754186897602</v>
+        <v>-388.8578473059474</v>
       </c>
       <c r="I10" t="n">
-        <v>-182.7291684390804</v>
+        <v>-381.808857131289</v>
       </c>
       <c r="J10" t="n">
-        <v>-210.2113947718159</v>
+        <v>-268.6921325461533</v>
       </c>
       <c r="K10" t="n">
-        <v>-269.209651321293</v>
+        <v>-370.0181476653877</v>
       </c>
       <c r="L10" t="n">
-        <v>-298.6447000845739</v>
+        <v>-392.9947767735325</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-3.306700140884343e-17</v>
+        <v>-1.98630755629672e-16</v>
       </c>
       <c r="B11" t="n">
-        <v>0.366540782828827</v>
+        <v>-2.337320515565135</v>
       </c>
       <c r="C11" t="n">
-        <v>1.476312830276173</v>
+        <v>-1.954832828469416</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2028757409776071</v>
+        <v>-0.2029562356079724</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007823538990350171</v>
+        <v>-0.007830148170738486</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-281.3685620372889</v>
+        <v>-265.4343525678009</v>
       </c>
       <c r="H11" t="n">
-        <v>-280.4087536240257</v>
+        <v>-366.6665302530839</v>
       </c>
       <c r="I11" t="n">
-        <v>-282.6744295386466</v>
+        <v>-257.9410806626655</v>
       </c>
       <c r="J11" t="n">
-        <v>-220.6441498996765</v>
+        <v>-428.9577688658146</v>
       </c>
       <c r="K11" t="n">
-        <v>-236.6576908197543</v>
+        <v>-484.3403404128372</v>
       </c>
       <c r="L11" t="n">
-        <v>-206.0416915890776</v>
+        <v>-490.2111601110895</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-172.7103297485407</v>
+        <v>-415.6732793505806</v>
       </c>
       <c r="H12" t="n">
-        <v>-186.3159208167994</v>
+        <v>-332.1190698111538</v>
       </c>
       <c r="I12" t="n">
-        <v>-110.1601648855138</v>
+        <v>-493.3320564668533</v>
       </c>
       <c r="J12" t="n">
-        <v>-275.0342298516327</v>
+        <v>-392.1240781879946</v>
       </c>
       <c r="K12" t="n">
-        <v>-189.4738739884041</v>
+        <v>-427.6690380284082</v>
       </c>
       <c r="L12" t="n">
-        <v>-249.3092308006451</v>
+        <v>-469.764413608158</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-172.7103297485407</v>
+        <v>-415.6732793505806</v>
       </c>
       <c r="H13" t="n">
-        <v>-186.3159208167994</v>
+        <v>-332.1190698111538</v>
       </c>
       <c r="I13" t="n">
-        <v>-110.1601648855138</v>
+        <v>-493.3320564668533</v>
       </c>
       <c r="J13" t="n">
-        <v>-275.0342298516327</v>
+        <v>-392.1240781879946</v>
       </c>
       <c r="K13" t="n">
-        <v>-189.4738739884041</v>
+        <v>-427.6690380284082</v>
       </c>
       <c r="L13" t="n">
-        <v>-249.3092308006451</v>
+        <v>-469.764413608158</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.063524445482365e-16</v>
+        <v>4.156315745383399e-16</v>
       </c>
       <c r="B15" t="n">
-        <v>6.637260372540447</v>
+        <v>7.28371711017866</v>
       </c>
       <c r="C15" t="n">
-        <v>2.17264233183042</v>
+        <v>2.172379884075227</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2031247678598138</v>
+        <v>0.2031254353518038</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007829986794926467</v>
+        <v>0.007830413205614567</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.156315745383399e-16</v>
+        <v>4.73722504211298e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>2.254949238885604</v>
+        <v>3.203646115624323</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.059240274666308</v>
+        <v>0.1112259055405668</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08698347905029004</v>
+        <v>-0.1690734890510618</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.002243622526310631</v>
+        <v>-0.003163778220487342</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-354.8169042986818</v>
+        <v>-499.6639982249136</v>
       </c>
       <c r="H2" t="n">
-        <v>-429.511816963417</v>
+        <v>-297.5173022443434</v>
       </c>
       <c r="I2" t="n">
-        <v>-269.5719452760135</v>
+        <v>-309.7916347825311</v>
       </c>
       <c r="J2" t="n">
-        <v>-505.7241886967951</v>
+        <v>-190.7921793328458</v>
       </c>
       <c r="K2" t="n">
-        <v>-437.9012958167249</v>
+        <v>-300.9147235258574</v>
       </c>
       <c r="L2" t="n">
-        <v>-428.810950591507</v>
+        <v>-192.4814796218298</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-3.492241176509067e-16</v>
+        <v>-3.562064473787729e-16</v>
       </c>
       <c r="B3" t="n">
-        <v>1.095981578202815</v>
+        <v>-0.3778973661195459</v>
       </c>
       <c r="C3" t="n">
-        <v>2.01235715961866</v>
+        <v>-1.841218599707578</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09327117689595858</v>
+        <v>0.1274363478919197</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002610700426912064</v>
+        <v>-0.004907047384638874</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-293.3306260360512</v>
+        <v>-350.7198558091643</v>
       </c>
       <c r="H3" t="n">
-        <v>-451.514793401242</v>
+        <v>-489.371102776032</v>
       </c>
       <c r="I3" t="n">
-        <v>-527.6275370456608</v>
+        <v>-509.7329763362149</v>
       </c>
       <c r="J3" t="n">
-        <v>-205.3309720683288</v>
+        <v>-493.7933328382941</v>
       </c>
       <c r="K3" t="n">
-        <v>-214.2538267976783</v>
+        <v>-440.8948219099566</v>
       </c>
       <c r="L3" t="n">
-        <v>-292.5052561886603</v>
+        <v>-287.8203541825995</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.742098362495043e-17</v>
+        <v>5.072228343796878e-19</v>
       </c>
       <c r="B4" t="n">
-        <v>7.28371711017866</v>
+        <v>7.26081075774644</v>
       </c>
       <c r="C4" t="n">
-        <v>2.165144638473163</v>
+        <v>2.14569648205008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1968891739082204</v>
+        <v>0.20294743746403</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.007149811023201835</v>
+        <v>0.007557603389631859</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-307.1206925993739</v>
+        <v>-506.0309371605395</v>
       </c>
       <c r="H4" t="n">
-        <v>-290.4918092779238</v>
+        <v>-469.9469895841947</v>
       </c>
       <c r="I4" t="n">
-        <v>-433.6065281525437</v>
+        <v>-295.3194117376828</v>
       </c>
       <c r="J4" t="n">
-        <v>-479.6953887603854</v>
+        <v>-205.787225671946</v>
       </c>
       <c r="K4" t="n">
-        <v>-525.2257521762867</v>
+        <v>-381.7681230526977</v>
       </c>
       <c r="L4" t="n">
-        <v>-518.1799601044149</v>
+        <v>-235.7430068630212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5.785026462574634e-17</v>
+        <v>-5.73943524479858e-17</v>
       </c>
       <c r="B5" t="n">
-        <v>-7.290727800952435</v>
+        <v>-7.283282190053392</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.172375568286604</v>
+        <v>-2.167405347830383</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2028678434365219</v>
+        <v>-0.2027763146522337</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004332958634543515</v>
+        <v>0.002558937438751546</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-477.6089246965869</v>
+        <v>-496.5530644694226</v>
       </c>
       <c r="H5" t="n">
-        <v>-408.642784880463</v>
+        <v>-408.9005457756559</v>
       </c>
       <c r="I5" t="n">
-        <v>-265.5485707280959</v>
+        <v>-519.0327803835905</v>
       </c>
       <c r="J5" t="n">
-        <v>-365.0694964038881</v>
+        <v>-385.2717196060852</v>
       </c>
       <c r="K5" t="n">
-        <v>-216.125888468655</v>
+        <v>-323.9081466033732</v>
       </c>
       <c r="L5" t="n">
-        <v>-494.6412523822127</v>
+        <v>-316.572133186045</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.468809157357587e-16</v>
+        <v>6.492392646159016e-17</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.492181493768099</v>
+        <v>1.966854080322581</v>
       </c>
       <c r="C6" t="n">
-        <v>2.172379884075227</v>
+        <v>2.172577999215413</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2029709606888156</v>
+        <v>0.2029629427194879</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.007146405796164886</v>
+        <v>0.00769698499555313</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-303.7171302886558</v>
+        <v>-383.494104373841</v>
       </c>
       <c r="H6" t="n">
-        <v>-478.7418864916751</v>
+        <v>-461.3585166405889</v>
       </c>
       <c r="I6" t="n">
-        <v>-211.4946424371041</v>
+        <v>-219.9613106061616</v>
       </c>
       <c r="J6" t="n">
-        <v>-398.6101779175913</v>
+        <v>-385.3282108315169</v>
       </c>
       <c r="K6" t="n">
-        <v>-484.0143052093359</v>
+        <v>-335.4290792720597</v>
       </c>
       <c r="L6" t="n">
-        <v>-342.2568006097193</v>
+        <v>-249.8164364632563</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.753489918413844e-16</v>
+        <v>8.517657641402115e-17</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.7625972340132381</v>
+        <v>-6.768054021058761</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.172393901095227</v>
+        <v>-2.172451127473945</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2028146438681043</v>
+        <v>-0.2028351443973495</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.005538069867868816</v>
+        <v>0.007609877777676778</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-191.6428436098091</v>
+        <v>-474.595004708436</v>
       </c>
       <c r="H7" t="n">
-        <v>-336.643783728227</v>
+        <v>-449.0695101145917</v>
       </c>
       <c r="I7" t="n">
-        <v>-233.5503730979178</v>
+        <v>-268.191622531273</v>
       </c>
       <c r="J7" t="n">
-        <v>-418.7777481352038</v>
+        <v>-278.153382999218</v>
       </c>
       <c r="K7" t="n">
-        <v>-282.2524730034239</v>
+        <v>-383.5230840252482</v>
       </c>
       <c r="L7" t="n">
-        <v>-347.713739820663</v>
+        <v>-413.0153194489037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.163612452399703e-17</v>
+        <v>2.004757525137446e-18</v>
       </c>
       <c r="B8" t="n">
-        <v>-5.249363050429602</v>
+        <v>0.3727023865615509</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3753966510173357</v>
+        <v>-1.357975495517268</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2031254353518038</v>
+        <v>0.2031252960299102</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.580030949281934e-05</v>
+        <v>-0.0005554946603836265</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-178.9524807817842</v>
+        <v>-329.9706397558758</v>
       </c>
       <c r="H8" t="n">
-        <v>-248.9527637782896</v>
+        <v>-498.9415031735107</v>
       </c>
       <c r="I8" t="n">
-        <v>-400.0480728539233</v>
+        <v>-427.5409927701043</v>
       </c>
       <c r="J8" t="n">
-        <v>-207.0835056689129</v>
+        <v>-348.14410930067</v>
       </c>
       <c r="K8" t="n">
-        <v>-348.1094845946809</v>
+        <v>-382.6306412535364</v>
       </c>
       <c r="L8" t="n">
-        <v>-446.4229447627749</v>
+        <v>-450.3146390615858</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-9.222398353653273e-17</v>
+        <v>-1.309099387540103e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>-5.132395539356654</v>
+        <v>-2.933489846937681</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3013650242668037</v>
+        <v>1.69363384721638</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2031238050562512</v>
+        <v>-0.2031254140237084</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009593615416338149</v>
+        <v>0.0005501575069012728</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-413.1892393297293</v>
+        <v>-323.3509112766465</v>
       </c>
       <c r="H9" t="n">
-        <v>-289.9317293084947</v>
+        <v>-203.9116710882615</v>
       </c>
       <c r="I9" t="n">
-        <v>-425.8009448246612</v>
+        <v>-188.5270732283834</v>
       </c>
       <c r="J9" t="n">
-        <v>-378.014728484413</v>
+        <v>-403.7532756405058</v>
       </c>
       <c r="K9" t="n">
-        <v>-221.0862106343696</v>
+        <v>-342.519767073772</v>
       </c>
       <c r="L9" t="n">
-        <v>-486.6983157389856</v>
+        <v>-354.5526215274361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-4.319810308768216e-17</v>
+        <v>-4.904102634856947e-17</v>
       </c>
       <c r="B10" t="n">
-        <v>-3.425176253716237</v>
+        <v>-4.427164329541238</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4810725166299394</v>
+        <v>0.5411657140883134</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2029457651895129</v>
+        <v>-0.2029336637974995</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007830413205614567</v>
+        <v>0.007830098411700369</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-204.0080771870923</v>
+        <v>-364.2319640904965</v>
       </c>
       <c r="H10" t="n">
-        <v>-388.8578473059474</v>
+        <v>-277.6036759814451</v>
       </c>
       <c r="I10" t="n">
-        <v>-381.808857131289</v>
+        <v>-393.920835950113</v>
       </c>
       <c r="J10" t="n">
-        <v>-268.6921325461533</v>
+        <v>-205.7799248992835</v>
       </c>
       <c r="K10" t="n">
-        <v>-370.0181476653877</v>
+        <v>-308.6816402879103</v>
       </c>
       <c r="L10" t="n">
-        <v>-392.9947767735325</v>
+        <v>-520.9276900782138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1.98630755629672e-16</v>
+        <v>-6.908124352411057e-17</v>
       </c>
       <c r="B11" t="n">
-        <v>-2.337320515565135</v>
+        <v>-3.394597066631371</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.954832828469416</v>
+        <v>1.671379403411398</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2029562356079724</v>
+        <v>-0.2029509325082046</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007830148170738486</v>
+        <v>-0.0078277050484522</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-265.4343525678009</v>
+        <v>-200.2469639188261</v>
       </c>
       <c r="H11" t="n">
-        <v>-366.6665302530839</v>
+        <v>-229.498715681002</v>
       </c>
       <c r="I11" t="n">
-        <v>-257.9410806626655</v>
+        <v>-361.7276882958779</v>
       </c>
       <c r="J11" t="n">
-        <v>-428.9577688658146</v>
+        <v>-401.1609552053811</v>
       </c>
       <c r="K11" t="n">
-        <v>-484.3403404128372</v>
+        <v>-450.3089049203305</v>
       </c>
       <c r="L11" t="n">
-        <v>-490.2111601110895</v>
+        <v>-297.3579742304087</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-415.6732793505806</v>
+        <v>-289.2883895482012</v>
       </c>
       <c r="H12" t="n">
-        <v>-332.1190698111538</v>
+        <v>-177.8553582262861</v>
       </c>
       <c r="I12" t="n">
-        <v>-493.3320564668533</v>
+        <v>-230.700804448371</v>
       </c>
       <c r="J12" t="n">
-        <v>-392.1240781879946</v>
+        <v>-186.818658866641</v>
       </c>
       <c r="K12" t="n">
-        <v>-427.6690380284082</v>
+        <v>-208.9755097582397</v>
       </c>
       <c r="L12" t="n">
-        <v>-469.764413608158</v>
+        <v>-463.4017058426597</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-415.6732793505806</v>
+        <v>-289.2883895482012</v>
       </c>
       <c r="H13" t="n">
-        <v>-332.1190698111538</v>
+        <v>-177.8553582262861</v>
       </c>
       <c r="I13" t="n">
-        <v>-493.3320564668533</v>
+        <v>-230.700804448371</v>
       </c>
       <c r="J13" t="n">
-        <v>-392.1240781879946</v>
+        <v>-186.818658866641</v>
       </c>
       <c r="K13" t="n">
-        <v>-427.6690380284082</v>
+        <v>-208.9755097582397</v>
       </c>
       <c r="L13" t="n">
-        <v>-469.764413608158</v>
+        <v>-463.4017058426597</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.156315745383399e-16</v>
+        <v>4.73722504211298e-16</v>
       </c>
       <c r="B15" t="n">
-        <v>7.28371711017866</v>
+        <v>7.26081075774644</v>
       </c>
       <c r="C15" t="n">
-        <v>2.172379884075227</v>
+        <v>2.172577999215413</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2031254353518038</v>
+        <v>0.2031252960299102</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007830413205614567</v>
+        <v>0.007830098411700369</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.73722504211298e-16</v>
+        <v>4.091402219407377e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>3.203646115624323</v>
+        <v>3.055503303417273</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1112259055405668</v>
+        <v>1.732034947384396</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1690734890510618</v>
+        <v>0.2007802082634225</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.003163778220487342</v>
+        <v>0.006188644216855313</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-499.6639982249136</v>
+        <v>235.2212983451001</v>
       </c>
       <c r="H2" t="n">
-        <v>-297.5173022443434</v>
+        <v>154.1500158816395</v>
       </c>
       <c r="I2" t="n">
-        <v>-309.7916347825311</v>
+        <v>229.9827586967068</v>
       </c>
       <c r="J2" t="n">
-        <v>-190.7921793328458</v>
+        <v>243.3897731718233</v>
       </c>
       <c r="K2" t="n">
-        <v>-300.9147235258574</v>
+        <v>194.9519682072257</v>
       </c>
       <c r="L2" t="n">
-        <v>-192.4814796218298</v>
+        <v>212.2485290368783</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-3.562064473787729e-16</v>
+        <v>-3.803898399444096e-16</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.3778973661195459</v>
+        <v>1.946855554106047</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.841218599707578</v>
+        <v>-1.843759210184875</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1274363478919197</v>
+        <v>-0.1835493982994691</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.004907047384638874</v>
+        <v>-0.001993192841362582</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-350.7198558091643</v>
+        <v>283.2323755089495</v>
       </c>
       <c r="H3" t="n">
-        <v>-489.371102776032</v>
+        <v>224.5044515745452</v>
       </c>
       <c r="I3" t="n">
-        <v>-509.7329763362149</v>
+        <v>268.5686654715594</v>
       </c>
       <c r="J3" t="n">
-        <v>-493.7933328382941</v>
+        <v>229.2500578626596</v>
       </c>
       <c r="K3" t="n">
-        <v>-440.8948219099566</v>
+        <v>107.27284664215</v>
       </c>
       <c r="L3" t="n">
-        <v>-287.8203541825995</v>
+        <v>171.7695117972128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.072228343796878e-19</v>
+        <v>-1.087024124102577e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>7.26081075774644</v>
+        <v>6.383847962420203</v>
       </c>
       <c r="C4" t="n">
-        <v>2.14569648205008</v>
+        <v>1.415453782885952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.20294743746403</v>
+        <v>0.2023303041251349</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007557603389631859</v>
+        <v>-0.001591208748088253</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-506.0309371605395</v>
+        <v>252.6791327241024</v>
       </c>
       <c r="H4" t="n">
-        <v>-469.9469895841947</v>
+        <v>142.127360533965</v>
       </c>
       <c r="I4" t="n">
-        <v>-295.3194117376828</v>
+        <v>112.0213867593917</v>
       </c>
       <c r="J4" t="n">
-        <v>-205.787225671946</v>
+        <v>296.1932018227483</v>
       </c>
       <c r="K4" t="n">
-        <v>-381.7681230526977</v>
+        <v>150.9117578934941</v>
       </c>
       <c r="L4" t="n">
-        <v>-235.7430068630212</v>
+        <v>285.1692146299674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5.73943524479858e-17</v>
+        <v>-2.471585942156827e-16</v>
       </c>
       <c r="B5" t="n">
-        <v>-7.283282190053392</v>
+        <v>-3.129840262806506</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.167405347830383</v>
+        <v>-2.063680658162722</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2027763146522337</v>
+        <v>-0.1930767728255319</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002558937438751546</v>
+        <v>0.001206372564489008</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-496.5530644694226</v>
+        <v>294.0521716091692</v>
       </c>
       <c r="H5" t="n">
-        <v>-408.9005457756559</v>
+        <v>105.8680120567771</v>
       </c>
       <c r="I5" t="n">
-        <v>-519.0327803835905</v>
+        <v>247.8094856972645</v>
       </c>
       <c r="J5" t="n">
-        <v>-385.2717196060852</v>
+        <v>206.449247629462</v>
       </c>
       <c r="K5" t="n">
-        <v>-323.9081466033732</v>
+        <v>134.8578781631891</v>
       </c>
       <c r="L5" t="n">
-        <v>-316.572133186045</v>
+        <v>128.707964038932</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6.492392646159016e-17</v>
+        <v>-3.225264426106674e-17</v>
       </c>
       <c r="B6" t="n">
-        <v>1.966854080322581</v>
+        <v>4.232745308826818</v>
       </c>
       <c r="C6" t="n">
-        <v>2.172577999215413</v>
+        <v>2.172130662493426</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2029629427194879</v>
+        <v>0.2026488309358206</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00769698499555313</v>
+        <v>0.007817997588955489</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-383.494104373841</v>
+        <v>263.4537320582812</v>
       </c>
       <c r="H6" t="n">
-        <v>-461.3585166405889</v>
+        <v>179.2151207829241</v>
       </c>
       <c r="I6" t="n">
-        <v>-219.9613106061616</v>
+        <v>287.7332103150164</v>
       </c>
       <c r="J6" t="n">
-        <v>-385.3282108315169</v>
+        <v>114.8845833110092</v>
       </c>
       <c r="K6" t="n">
-        <v>-335.4290792720597</v>
+        <v>178.2047393955353</v>
       </c>
       <c r="L6" t="n">
-        <v>-249.8164364632563</v>
+        <v>283.4299800911605</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.517657641402115e-17</v>
+        <v>-1.198172884133362e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>-6.768054021058761</v>
+        <v>2.576064671916451</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.172451127473945</v>
+        <v>-2.172516786081878</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2028351443973495</v>
+        <v>-0.2029358350451315</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007609877777676778</v>
+        <v>-0.004911098508484864</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-474.595004708436</v>
+        <v>121.7487930734277</v>
       </c>
       <c r="H7" t="n">
-        <v>-449.0695101145917</v>
+        <v>142.6316026076196</v>
       </c>
       <c r="I7" t="n">
-        <v>-268.191622531273</v>
+        <v>138.4936312060727</v>
       </c>
       <c r="J7" t="n">
-        <v>-278.153382999218</v>
+        <v>194.0098947973537</v>
       </c>
       <c r="K7" t="n">
-        <v>-383.5230840252482</v>
+        <v>133.1386858321638</v>
       </c>
       <c r="L7" t="n">
-        <v>-413.0153194489037</v>
+        <v>180.7483017453656</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.004757525137446e-18</v>
+        <v>-2.672298253781471e-17</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3727023865615509</v>
+        <v>4.549693012353724</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.357975495517268</v>
+        <v>-0.563372943088447</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2031252960299102</v>
+        <v>0.2031052586107497</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0005554946603836265</v>
+        <v>0.001946466232204936</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-329.9706397558758</v>
+        <v>127.7573892925534</v>
       </c>
       <c r="H8" t="n">
-        <v>-498.9415031735107</v>
+        <v>283.5229704323186</v>
       </c>
       <c r="I8" t="n">
-        <v>-427.5409927701043</v>
+        <v>109.1967867457293</v>
       </c>
       <c r="J8" t="n">
-        <v>-348.14410930067</v>
+        <v>232.317487024862</v>
       </c>
       <c r="K8" t="n">
-        <v>-382.6306412535364</v>
+        <v>198.0156415859207</v>
       </c>
       <c r="L8" t="n">
-        <v>-450.3146390615858</v>
+        <v>299.4690796159133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1.309099387540103e-17</v>
+        <v>-8.82585860985017e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>-2.933489846937681</v>
+        <v>-1.441372094549233</v>
       </c>
       <c r="C9" t="n">
-        <v>1.69363384721638</v>
+        <v>-1.849935776345166</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2031254140237084</v>
+        <v>-0.203113010028629</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0005501575069012728</v>
+        <v>-0.002203801592632328</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-323.3509112766465</v>
+        <v>176.4130725822592</v>
       </c>
       <c r="H9" t="n">
-        <v>-203.9116710882615</v>
+        <v>245.713050886135</v>
       </c>
       <c r="I9" t="n">
-        <v>-188.5270732283834</v>
+        <v>117.1596281347101</v>
       </c>
       <c r="J9" t="n">
-        <v>-403.7532756405058</v>
+        <v>288.8138278404767</v>
       </c>
       <c r="K9" t="n">
-        <v>-342.519767073772</v>
+        <v>258.0456512981706</v>
       </c>
       <c r="L9" t="n">
-        <v>-354.5526215274361</v>
+        <v>248.8715905944032</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-4.904102634856947e-17</v>
+        <v>1.403255602090964e-16</v>
       </c>
       <c r="B10" t="n">
-        <v>-4.427164329541238</v>
+        <v>3.594878788844059</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5411657140883134</v>
+        <v>2.16522938234038</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2029336637974995</v>
+        <v>0.2029505616889527</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007830098411700369</v>
+        <v>0.007828303734870886</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-364.2319640904965</v>
+        <v>168.0841434123181</v>
       </c>
       <c r="H10" t="n">
-        <v>-277.6036759814451</v>
+        <v>228.7006329939168</v>
       </c>
       <c r="I10" t="n">
-        <v>-393.920835950113</v>
+        <v>245.7353302695956</v>
       </c>
       <c r="J10" t="n">
-        <v>-205.7799248992835</v>
+        <v>125.1154989629193</v>
       </c>
       <c r="K10" t="n">
-        <v>-308.6816402879103</v>
+        <v>134.9351659490707</v>
       </c>
       <c r="L10" t="n">
-        <v>-520.9276900782138</v>
+        <v>264.6585282886405</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-6.908124352411057e-17</v>
+        <v>-5.998515593512319e-17</v>
       </c>
       <c r="B11" t="n">
-        <v>-3.394597066631371</v>
+        <v>-2.79276373427344</v>
       </c>
       <c r="C11" t="n">
-        <v>1.671379403411398</v>
+        <v>-2.143502973102945</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2029509325082046</v>
+        <v>-0.2029569121361087</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0078277050484522</v>
+        <v>-0.007830464215228134</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-200.2469639188261</v>
+        <v>103.1660510073546</v>
       </c>
       <c r="H11" t="n">
-        <v>-229.498715681002</v>
+        <v>283.2681422643896</v>
       </c>
       <c r="I11" t="n">
-        <v>-361.7276882958779</v>
+        <v>149.5838285754555</v>
       </c>
       <c r="J11" t="n">
-        <v>-401.1609552053811</v>
+        <v>280.7465981665982</v>
       </c>
       <c r="K11" t="n">
-        <v>-450.3089049203305</v>
+        <v>164.6393742083581</v>
       </c>
       <c r="L11" t="n">
-        <v>-297.3579742304087</v>
+        <v>267.6604337665934</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-289.2883895482012</v>
+        <v>217.577369532687</v>
       </c>
       <c r="H12" t="n">
-        <v>-177.8553582262861</v>
+        <v>179.3695940583734</v>
       </c>
       <c r="I12" t="n">
-        <v>-230.700804448371</v>
+        <v>282.4701161580262</v>
       </c>
       <c r="J12" t="n">
-        <v>-186.818658866641</v>
+        <v>242.819519033292</v>
       </c>
       <c r="K12" t="n">
-        <v>-208.9755097582397</v>
+        <v>169.0397098943142</v>
       </c>
       <c r="L12" t="n">
-        <v>-463.4017058426597</v>
+        <v>266.3169533656837</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-289.2883895482012</v>
+        <v>217.577369532687</v>
       </c>
       <c r="H13" t="n">
-        <v>-177.8553582262861</v>
+        <v>179.3695940583734</v>
       </c>
       <c r="I13" t="n">
-        <v>-230.700804448371</v>
+        <v>282.4701161580262</v>
       </c>
       <c r="J13" t="n">
-        <v>-186.818658866641</v>
+        <v>242.819519033292</v>
       </c>
       <c r="K13" t="n">
-        <v>-208.9755097582397</v>
+        <v>169.0397098943142</v>
       </c>
       <c r="L13" t="n">
-        <v>-463.4017058426597</v>
+        <v>266.3169533656837</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.73722504211298e-16</v>
+        <v>4.091402219407377e-16</v>
       </c>
       <c r="B15" t="n">
-        <v>7.26081075774644</v>
+        <v>6.383847962420203</v>
       </c>
       <c r="C15" t="n">
-        <v>2.172577999215413</v>
+        <v>2.172130662493426</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2031252960299102</v>
+        <v>0.2031052586107497</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007830098411700369</v>
+        <v>0.007828303734870886</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.091402219407377e-16</v>
+        <v>9.104388445183871e-15</v>
       </c>
       <c r="B2" t="n">
-        <v>3.055503303417273</v>
+        <v>32.64551197903957</v>
       </c>
       <c r="C2" t="n">
-        <v>1.732034947384396</v>
+        <v>9.915228732075025</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2007802082634225</v>
+        <v>-4.301901556911651</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006188644216855313</v>
+        <v>0.2632062314314525</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>235.2212983451001</v>
+        <v>-428.9129351365891</v>
       </c>
       <c r="H2" t="n">
-        <v>154.1500158816395</v>
+        <v>-441.6669630005811</v>
       </c>
       <c r="I2" t="n">
-        <v>229.9827586967068</v>
+        <v>-182.8480606248464</v>
       </c>
       <c r="J2" t="n">
-        <v>243.3897731718233</v>
+        <v>-260.260263704629</v>
       </c>
       <c r="K2" t="n">
-        <v>194.9519682072257</v>
+        <v>-237.4441081525978</v>
       </c>
       <c r="L2" t="n">
-        <v>212.2485290368783</v>
+        <v>-224.5935305570712</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-3.803898399444096e-16</v>
+        <v>-6.665904824229744e-15</v>
       </c>
       <c r="B3" t="n">
-        <v>1.946855554106047</v>
+        <v>-29.08468820755509</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.843759210184875</v>
+        <v>-10.7719652242274</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1835493982994691</v>
+        <v>4.620230246203703</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001993192841362582</v>
+        <v>0.2967592060196742</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>283.2323755089495</v>
+        <v>-477.999861559083</v>
       </c>
       <c r="H3" t="n">
-        <v>224.5044515745452</v>
+        <v>-529.9043288688383</v>
       </c>
       <c r="I3" t="n">
-        <v>268.5686654715594</v>
+        <v>-382.2266014371806</v>
       </c>
       <c r="J3" t="n">
-        <v>229.2500578626596</v>
+        <v>-215.4674697224137</v>
       </c>
       <c r="K3" t="n">
-        <v>107.27284664215</v>
+        <v>-394.0348429875706</v>
       </c>
       <c r="L3" t="n">
-        <v>171.7695117972128</v>
+        <v>-335.7993447836358</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.087024124102577e-16</v>
+        <v>1.418685096290753e-15</v>
       </c>
       <c r="B4" t="n">
-        <v>6.383847962420203</v>
+        <v>44.92646741503364</v>
       </c>
       <c r="C4" t="n">
-        <v>1.415453782885952</v>
+        <v>21.20904542553595</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2023303041251349</v>
+        <v>4.58852898297232</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.001591208748088253</v>
+        <v>0.08727293184632624</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>252.6791327241024</v>
+        <v>-191.6595284597668</v>
       </c>
       <c r="H4" t="n">
-        <v>142.127360533965</v>
+        <v>-383.0509766251732</v>
       </c>
       <c r="I4" t="n">
-        <v>112.0213867593917</v>
+        <v>-255.1468797131511</v>
       </c>
       <c r="J4" t="n">
-        <v>296.1932018227483</v>
+        <v>-255.0471135297751</v>
       </c>
       <c r="K4" t="n">
-        <v>150.9117578934941</v>
+        <v>-331.4463386259168</v>
       </c>
       <c r="L4" t="n">
-        <v>285.1692146299674</v>
+        <v>-349.3133954616054</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-2.471585942156827e-16</v>
+        <v>-2.804871875712734e-15</v>
       </c>
       <c r="B5" t="n">
-        <v>-3.129840262806506</v>
+        <v>-44.90046805978162</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.063680658162722</v>
+        <v>-21.19089301163933</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1930767728255319</v>
+        <v>-4.574702066714449</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001206372564489008</v>
+        <v>-0.2192403034779217</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>294.0521716091692</v>
+        <v>-517.9238222207166</v>
       </c>
       <c r="H5" t="n">
-        <v>105.8680120567771</v>
+        <v>-201.1290686061716</v>
       </c>
       <c r="I5" t="n">
-        <v>247.8094856972645</v>
+        <v>-222.8084008188774</v>
       </c>
       <c r="J5" t="n">
-        <v>206.449247629462</v>
+        <v>-400.25698458312</v>
       </c>
       <c r="K5" t="n">
-        <v>134.8578781631891</v>
+        <v>-460.4471966557766</v>
       </c>
       <c r="L5" t="n">
-        <v>128.707964038932</v>
+        <v>-190.0994281255506</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-3.225264426106674e-17</v>
+        <v>6.86148482467858e-16</v>
       </c>
       <c r="B6" t="n">
-        <v>4.232745308826818</v>
+        <v>22.08444586936353</v>
       </c>
       <c r="C6" t="n">
-        <v>2.172130662493426</v>
+        <v>21.25160621330359</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2026488309358206</v>
+        <v>4.629732143960847</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007817997588955489</v>
+        <v>-0.08936922553548789</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>263.4537320582812</v>
+        <v>-420.4489520841011</v>
       </c>
       <c r="H6" t="n">
-        <v>179.2151207829241</v>
+        <v>-277.8229082314253</v>
       </c>
       <c r="I6" t="n">
-        <v>287.7332103150164</v>
+        <v>-198.737569734517</v>
       </c>
       <c r="J6" t="n">
-        <v>114.8845833110092</v>
+        <v>-344.325445851012</v>
       </c>
       <c r="K6" t="n">
-        <v>178.2047393955353</v>
+        <v>-476.9498836376345</v>
       </c>
       <c r="L6" t="n">
-        <v>283.4299800911605</v>
+        <v>-235.4875486765571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.198172884133362e-16</v>
+        <v>-2.421023149963933e-15</v>
       </c>
       <c r="B7" t="n">
-        <v>2.576064671916451</v>
+        <v>-43.16457213180438</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.172516786081878</v>
+        <v>-21.25804046506167</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2029358350451315</v>
+        <v>-4.630473233858812</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.004911098508484864</v>
+        <v>-0.1087963583830271</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>121.7487930734277</v>
+        <v>-230.7908341164119</v>
       </c>
       <c r="H7" t="n">
-        <v>142.6316026076196</v>
+        <v>-349.136596205125</v>
       </c>
       <c r="I7" t="n">
-        <v>138.4936312060727</v>
+        <v>-184.6543208482451</v>
       </c>
       <c r="J7" t="n">
-        <v>194.0098947973537</v>
+        <v>-437.05808394255</v>
       </c>
       <c r="K7" t="n">
-        <v>133.1386858321638</v>
+        <v>-403.1223776765412</v>
       </c>
       <c r="L7" t="n">
-        <v>180.7483017453656</v>
+        <v>-350.3828095088444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-2.672298253781471e-17</v>
+        <v>-1.130364759093825e-17</v>
       </c>
       <c r="B8" t="n">
-        <v>4.549693012353724</v>
+        <v>-14.68965693483734</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.563372943088447</v>
+        <v>3.926111335781985</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2031052586107497</v>
+        <v>4.633406840059772</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001946466232204936</v>
+        <v>0.02485054002967271</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>127.7573892925534</v>
+        <v>-208.5012359599034</v>
       </c>
       <c r="H8" t="n">
-        <v>283.5229704323186</v>
+        <v>-341.8425548008991</v>
       </c>
       <c r="I8" t="n">
-        <v>109.1967867457293</v>
+        <v>-186.2172085073458</v>
       </c>
       <c r="J8" t="n">
-        <v>232.317487024862</v>
+        <v>-382.6580209147443</v>
       </c>
       <c r="K8" t="n">
-        <v>198.0156415859207</v>
+        <v>-312.2093193225955</v>
       </c>
       <c r="L8" t="n">
-        <v>299.4690796159133</v>
+        <v>-434.1623008966967</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-8.82585860985017e-17</v>
+        <v>2.732717759893393e-16</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.441372094549233</v>
+        <v>-17.29471475854365</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.849935776345166</v>
+        <v>5.645992011700238</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.203113010028629</v>
+        <v>-4.633476729841666</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.002203801592632328</v>
+        <v>0.005484267575969232</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>176.4130725822592</v>
+        <v>-485.230521565346</v>
       </c>
       <c r="H9" t="n">
-        <v>245.713050886135</v>
+        <v>-299.9499523747959</v>
       </c>
       <c r="I9" t="n">
-        <v>117.1596281347101</v>
+        <v>-276.3388032010915</v>
       </c>
       <c r="J9" t="n">
-        <v>288.8138278404767</v>
+        <v>-423.4428478059036</v>
       </c>
       <c r="K9" t="n">
-        <v>258.0456512981706</v>
+        <v>-369.1889950577624</v>
       </c>
       <c r="L9" t="n">
-        <v>248.8715905944032</v>
+        <v>-453.7634920769354</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.403255602090964e-16</v>
+        <v>-5.705335297112607e-17</v>
       </c>
       <c r="B10" t="n">
-        <v>3.594878788844059</v>
+        <v>-29.94186068420492</v>
       </c>
       <c r="C10" t="n">
-        <v>2.16522938234038</v>
+        <v>-19.16495609370927</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2029505616889527</v>
+        <v>-4.617349479644658</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007828303734870886</v>
+        <v>0.3845658947060088</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>168.0841434123181</v>
+        <v>-418.8655458108279</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7006329939168</v>
+        <v>-515.0594987553229</v>
       </c>
       <c r="I10" t="n">
-        <v>245.7353302695956</v>
+        <v>-424.0351855449985</v>
       </c>
       <c r="J10" t="n">
-        <v>125.1154989629193</v>
+        <v>-450.9944494077973</v>
       </c>
       <c r="K10" t="n">
-        <v>134.9351659490707</v>
+        <v>-370.8687009722331</v>
       </c>
       <c r="L10" t="n">
-        <v>264.6585282886405</v>
+        <v>-298.9664938568845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-5.998515593512319e-17</v>
+        <v>2.431045331858758e-16</v>
       </c>
       <c r="B11" t="n">
-        <v>-2.79276373427344</v>
+        <v>-25.03991040162575</v>
       </c>
       <c r="C11" t="n">
-        <v>-2.143502973102945</v>
+        <v>-11.93610666351913</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2029569121361087</v>
+        <v>4.617125107766179</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007830464215228134</v>
+        <v>-0.3845368936335546</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>103.1660510073546</v>
+        <v>-384.9202164020329</v>
       </c>
       <c r="H11" t="n">
-        <v>283.2681422643896</v>
+        <v>-311.5426618107471</v>
       </c>
       <c r="I11" t="n">
-        <v>149.5838285754555</v>
+        <v>-324.8761326079853</v>
       </c>
       <c r="J11" t="n">
-        <v>280.7465981665982</v>
+        <v>-256.198600958662</v>
       </c>
       <c r="K11" t="n">
-        <v>164.6393742083581</v>
+        <v>-386.482263176634</v>
       </c>
       <c r="L11" t="n">
-        <v>267.6604337665934</v>
+        <v>-429.5194055463011</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>217.577369532687</v>
+        <v>-212.028396669866</v>
       </c>
       <c r="H12" t="n">
-        <v>179.3695940583734</v>
+        <v>-188.5880678237847</v>
       </c>
       <c r="I12" t="n">
-        <v>282.4701161580262</v>
+        <v>-251.7637608948216</v>
       </c>
       <c r="J12" t="n">
-        <v>242.819519033292</v>
+        <v>-361.6728006342437</v>
       </c>
       <c r="K12" t="n">
-        <v>169.0397098943142</v>
+        <v>-222.7257928930196</v>
       </c>
       <c r="L12" t="n">
-        <v>266.3169533656837</v>
+        <v>-428.2809009150786</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>217.577369532687</v>
+        <v>-212.028396669866</v>
       </c>
       <c r="H13" t="n">
-        <v>179.3695940583734</v>
+        <v>-188.5880678237847</v>
       </c>
       <c r="I13" t="n">
-        <v>282.4701161580262</v>
+        <v>-251.7637608948216</v>
       </c>
       <c r="J13" t="n">
-        <v>242.819519033292</v>
+        <v>-361.6728006342437</v>
       </c>
       <c r="K13" t="n">
-        <v>169.0397098943142</v>
+        <v>-222.7257928930196</v>
       </c>
       <c r="L13" t="n">
-        <v>266.3169533656837</v>
+        <v>-428.2809009150786</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.091402219407377e-16</v>
+        <v>9.104388445183871e-15</v>
       </c>
       <c r="B15" t="n">
-        <v>6.383847962420203</v>
+        <v>44.92646741503364</v>
       </c>
       <c r="C15" t="n">
-        <v>2.172130662493426</v>
+        <v>21.25160621330359</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2031052586107497</v>
+        <v>4.633406840059772</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007828303734870886</v>
+        <v>0.3845658947060088</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -480,382 +480,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9.104388445183871e-15</v>
+        <v>1.158017126043946e-14</v>
       </c>
       <c r="B2" t="n">
-        <v>32.64551197903957</v>
+        <v>65.82558654127374</v>
       </c>
       <c r="C2" t="n">
-        <v>9.915228732075025</v>
+        <v>33.49117113228255</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.301901556911651</v>
+        <v>4.344919915176486</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2632062314314525</v>
+        <v>0.2460370657452163</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-428.9129351365891</v>
+        <v>-307.1858820271387</v>
       </c>
       <c r="H2" t="n">
-        <v>-441.6669630005811</v>
+        <v>-337.130388551705</v>
       </c>
       <c r="I2" t="n">
-        <v>-182.8480606248464</v>
+        <v>-355.8953571847187</v>
       </c>
       <c r="J2" t="n">
-        <v>-260.260263704629</v>
+        <v>-415.7000194993333</v>
       </c>
       <c r="K2" t="n">
-        <v>-237.4441081525978</v>
+        <v>-495.4742371569654</v>
       </c>
       <c r="L2" t="n">
-        <v>-224.5935305570712</v>
+        <v>-492.5004462791052</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-6.665904824229744e-15</v>
+        <v>-1.201723443584241e-14</v>
       </c>
       <c r="B3" t="n">
-        <v>-29.08468820755509</v>
+        <v>-62.08457910089774</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.7719652242274</v>
+        <v>-23.48720362495549</v>
       </c>
       <c r="D3" t="n">
-        <v>4.620230246203703</v>
+        <v>-4.36766591826008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2967592060196742</v>
+        <v>0.2693156030309629</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-477.999861559083</v>
+        <v>-186.6041345315526</v>
       </c>
       <c r="H3" t="n">
-        <v>-529.9043288688383</v>
+        <v>-195.8058489108338</v>
       </c>
       <c r="I3" t="n">
-        <v>-382.2266014371806</v>
+        <v>-379.1197653694511</v>
       </c>
       <c r="J3" t="n">
-        <v>-215.4674697224137</v>
+        <v>-276.3008052942993</v>
       </c>
       <c r="K3" t="n">
-        <v>-394.0348429875706</v>
+        <v>-322.3515312294784</v>
       </c>
       <c r="L3" t="n">
-        <v>-335.7993447836358</v>
+        <v>-308.3608103848833</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.418685096290753e-15</v>
+        <v>1.457349728839013e-15</v>
       </c>
       <c r="B4" t="n">
-        <v>44.92646741503364</v>
+        <v>72.75488570955555</v>
       </c>
       <c r="C4" t="n">
-        <v>21.20904542553595</v>
+        <v>34.23745756584223</v>
       </c>
       <c r="D4" t="n">
-        <v>4.58852898297232</v>
+        <v>4.617280560125621</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08727293184632624</v>
+        <v>-0.007553968119399785</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-191.6595284597668</v>
+        <v>-472.6376975985629</v>
       </c>
       <c r="H4" t="n">
-        <v>-383.0509766251732</v>
+        <v>-332.3410167754608</v>
       </c>
       <c r="I4" t="n">
-        <v>-255.1468797131511</v>
+        <v>-216.7363583584817</v>
       </c>
       <c r="J4" t="n">
-        <v>-255.0471135297751</v>
+        <v>-286.6285717259553</v>
       </c>
       <c r="K4" t="n">
-        <v>-331.4463386259168</v>
+        <v>-370.6971102675043</v>
       </c>
       <c r="L4" t="n">
-        <v>-349.3133954616054</v>
+        <v>-403.2383101266166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-2.804871875712734e-15</v>
+        <v>4.131642017706478e-16</v>
       </c>
       <c r="B5" t="n">
-        <v>-44.90046805978162</v>
+        <v>-72.57703256250767</v>
       </c>
       <c r="C5" t="n">
-        <v>-21.19089301163933</v>
+        <v>-34.15898977735446</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.574702066714449</v>
+        <v>-4.550929549321958</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2192403034779217</v>
+        <v>0.1365951122419682</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-517.9238222207166</v>
+        <v>-429.9379982708162</v>
       </c>
       <c r="H5" t="n">
-        <v>-201.1290686061716</v>
+        <v>-486.2816184536979</v>
       </c>
       <c r="I5" t="n">
-        <v>-222.8084008188774</v>
+        <v>-186.9257613804342</v>
       </c>
       <c r="J5" t="n">
-        <v>-400.25698458312</v>
+        <v>-413.6107369559951</v>
       </c>
       <c r="K5" t="n">
-        <v>-460.4471966557766</v>
+        <v>-464.1608131858724</v>
       </c>
       <c r="L5" t="n">
-        <v>-190.0994281255506</v>
+        <v>-308.4628068165857</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6.86148482467858e-16</v>
+        <v>-2.586856717787989e-16</v>
       </c>
       <c r="B6" t="n">
-        <v>22.08444586936353</v>
+        <v>-0.5983940329453121</v>
       </c>
       <c r="C6" t="n">
-        <v>21.25160621330359</v>
+        <v>34.27487797097394</v>
       </c>
       <c r="D6" t="n">
-        <v>4.629732143960847</v>
+        <v>4.627055717275937</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08936922553548789</v>
+        <v>0.1993669690983227</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-420.4489520841011</v>
+        <v>-277.5879127195409</v>
       </c>
       <c r="H6" t="n">
-        <v>-277.8229082314253</v>
+        <v>-317.091171969849</v>
       </c>
       <c r="I6" t="n">
-        <v>-198.737569734517</v>
+        <v>-386.2729667306222</v>
       </c>
       <c r="J6" t="n">
-        <v>-344.325445851012</v>
+        <v>-332.9102484155094</v>
       </c>
       <c r="K6" t="n">
-        <v>-476.9498836376345</v>
+        <v>-245.6896068973816</v>
       </c>
       <c r="L6" t="n">
-        <v>-235.4875486765571</v>
+        <v>-199.6462680349517</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-2.421023149963933e-15</v>
+        <v>2.234894165599741e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>-43.16457213180438</v>
+        <v>-61.6228854673481</v>
       </c>
       <c r="C7" t="n">
-        <v>-21.25804046506167</v>
+        <v>-34.28187711272829</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.630473233858812</v>
+        <v>-4.632296312104169</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1087963583830271</v>
+        <v>-0.01594674427689886</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-230.7908341164119</v>
+        <v>-459.1254092749147</v>
       </c>
       <c r="H7" t="n">
-        <v>-349.136596205125</v>
+        <v>-220.8499334632698</v>
       </c>
       <c r="I7" t="n">
-        <v>-184.6543208482451</v>
+        <v>-476.4915834131096</v>
       </c>
       <c r="J7" t="n">
-        <v>-437.05808394255</v>
+        <v>-486.1209820702944</v>
       </c>
       <c r="K7" t="n">
-        <v>-403.1223776765412</v>
+        <v>-356.5865921431373</v>
       </c>
       <c r="L7" t="n">
-        <v>-350.3828095088444</v>
+        <v>-297.8344952251817</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.130364759093825e-17</v>
+        <v>6.516266488591893e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>-14.68965693483734</v>
+        <v>-21.9945015396075</v>
       </c>
       <c r="C8" t="n">
-        <v>3.926111335781985</v>
+        <v>14.70241039399864</v>
       </c>
       <c r="D8" t="n">
-        <v>4.633406840059772</v>
+        <v>4.633380754714922</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02485054002967271</v>
+        <v>-0.024105811999669</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-208.5012359599034</v>
+        <v>-282.7392712665126</v>
       </c>
       <c r="H8" t="n">
-        <v>-341.8425548008991</v>
+        <v>-244.4867908893632</v>
       </c>
       <c r="I8" t="n">
-        <v>-186.2172085073458</v>
+        <v>-286.0860656076363</v>
       </c>
       <c r="J8" t="n">
-        <v>-382.6580209147443</v>
+        <v>-477.3969742148799</v>
       </c>
       <c r="K8" t="n">
-        <v>-312.2093193225955</v>
+        <v>-440.6455081329881</v>
       </c>
       <c r="L8" t="n">
-        <v>-434.1623008966967</v>
+        <v>-404.0443097978236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.732717759893393e-16</v>
+        <v>-2.273091110257183e-16</v>
       </c>
       <c r="B9" t="n">
-        <v>-17.29471475854365</v>
+        <v>61.56050512277194</v>
       </c>
       <c r="C9" t="n">
-        <v>5.645992011700238</v>
+        <v>24.1379722413469</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.633476729841666</v>
+        <v>-4.633211881034514</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005484267575969232</v>
+        <v>-0.03280685946515912</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-485.230521565346</v>
+        <v>-483.2724634039739</v>
       </c>
       <c r="H9" t="n">
-        <v>-299.9499523747959</v>
+        <v>-196.5170722533677</v>
       </c>
       <c r="I9" t="n">
-        <v>-276.3388032010915</v>
+        <v>-269.3900503189717</v>
       </c>
       <c r="J9" t="n">
-        <v>-423.4428478059036</v>
+        <v>-436.739156961807</v>
       </c>
       <c r="K9" t="n">
-        <v>-369.1889950577624</v>
+        <v>-471.6976033358526</v>
       </c>
       <c r="L9" t="n">
-        <v>-453.7634920769354</v>
+        <v>-320.5849019083331</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-5.705335297112607e-17</v>
+        <v>-2.287502100180515e-16</v>
       </c>
       <c r="B10" t="n">
-        <v>-29.94186068420492</v>
+        <v>21.64807069891622</v>
       </c>
       <c r="C10" t="n">
-        <v>-19.16495609370927</v>
+        <v>24.6199410785954</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.617349479644658</v>
+        <v>-4.617437489580903</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3845658947060088</v>
+        <v>0.3845187133700474</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-418.8655458108279</v>
+        <v>-441.4496276851401</v>
       </c>
       <c r="H10" t="n">
-        <v>-515.0594987553229</v>
+        <v>-510.5948830167984</v>
       </c>
       <c r="I10" t="n">
-        <v>-424.0351855449985</v>
+        <v>-495.9386559183077</v>
       </c>
       <c r="J10" t="n">
-        <v>-450.9944494077973</v>
+        <v>-193.0822109907045</v>
       </c>
       <c r="K10" t="n">
-        <v>-370.8687009722331</v>
+        <v>-317.7947808786281</v>
       </c>
       <c r="L10" t="n">
-        <v>-298.9664938568845</v>
+        <v>-258.7246384229464</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2.431045331858758e-16</v>
+        <v>-3.161693472825149e-17</v>
       </c>
       <c r="B11" t="n">
-        <v>-25.03991040162575</v>
+        <v>-20.46079347430157</v>
       </c>
       <c r="C11" t="n">
-        <v>-11.93610666351913</v>
+        <v>16.59279036407499</v>
       </c>
       <c r="D11" t="n">
-        <v>4.617125107766179</v>
+        <v>-4.617363830806576</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3845368936335546</v>
+        <v>-0.3845346664407691</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-384.9202164020329</v>
+        <v>-372.1531707410059</v>
       </c>
       <c r="H11" t="n">
-        <v>-311.5426618107471</v>
+        <v>-244.7141334004037</v>
       </c>
       <c r="I11" t="n">
-        <v>-324.8761326079853</v>
+        <v>-331.1444019380936</v>
       </c>
       <c r="J11" t="n">
-        <v>-256.198600958662</v>
+        <v>-519.2045320418721</v>
       </c>
       <c r="K11" t="n">
-        <v>-386.482263176634</v>
+        <v>-178.2864822662269</v>
       </c>
       <c r="L11" t="n">
-        <v>-429.5194055463011</v>
+        <v>-434.1738024232443</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-212.028396669866</v>
+        <v>-214.4828959350884</v>
       </c>
       <c r="H12" t="n">
-        <v>-188.5880678237847</v>
+        <v>-423.4693951614913</v>
       </c>
       <c r="I12" t="n">
-        <v>-251.7637608948216</v>
+        <v>-494.3416955883869</v>
       </c>
       <c r="J12" t="n">
-        <v>-361.6728006342437</v>
+        <v>-431.8516367298919</v>
       </c>
       <c r="K12" t="n">
-        <v>-222.7257928930196</v>
+        <v>-342.8861601677124</v>
       </c>
       <c r="L12" t="n">
-        <v>-428.2809009150786</v>
+        <v>-226.7334697377379</v>
       </c>
     </row>
     <row r="13">
@@ -916,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-212.028396669866</v>
+        <v>-214.4828959350884</v>
       </c>
       <c r="H13" t="n">
-        <v>-188.5880678237847</v>
+        <v>-423.4693951614913</v>
       </c>
       <c r="I13" t="n">
-        <v>-251.7637608948216</v>
+        <v>-494.3416955883869</v>
       </c>
       <c r="J13" t="n">
-        <v>-361.6728006342437</v>
+        <v>-431.8516367298919</v>
       </c>
       <c r="K13" t="n">
-        <v>-222.7257928930196</v>
+        <v>-342.8861601677124</v>
       </c>
       <c r="L13" t="n">
-        <v>-428.2809009150786</v>
+        <v>-226.7334697377379</v>
       </c>
     </row>
     <row r="14">
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9.104388445183871e-15</v>
+        <v>1.158017126043946e-14</v>
       </c>
       <c r="B15" t="n">
-        <v>44.92646741503364</v>
+        <v>72.75488570955555</v>
       </c>
       <c r="C15" t="n">
-        <v>21.25160621330359</v>
+        <v>34.27487797097394</v>
       </c>
       <c r="D15" t="n">
-        <v>4.633406840059772</v>
+        <v>4.633380754714922</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3845658947060088</v>
+        <v>0.3845187133700474</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,540 +449,718 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>torque 7</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>angle 1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>angle 2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>angle 3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>angle 4</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>angle 5</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>angle 6</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>angle 7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.158017126043946e-14</v>
+        <v>7.135609487268385e-15</v>
       </c>
       <c r="B2" t="n">
-        <v>65.82558654127374</v>
+        <v>22.25049312448555</v>
       </c>
       <c r="C2" t="n">
-        <v>33.49117113228255</v>
+        <v>-4.867269527210841</v>
       </c>
       <c r="D2" t="n">
-        <v>4.344919915176486</v>
+        <v>-8.121035634862352</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2460370657452163</v>
+        <v>-1.942561558001296</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-2.521310373174949</v>
       </c>
       <c r="G2" t="n">
-        <v>-307.1858820271387</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-337.130388551705</v>
+        <v>209.7898304122282</v>
       </c>
       <c r="I2" t="n">
-        <v>-355.8953571847187</v>
+        <v>517.5408897157441</v>
       </c>
       <c r="J2" t="n">
-        <v>-415.7000194993333</v>
+        <v>516.7933625052171</v>
       </c>
       <c r="K2" t="n">
-        <v>-495.4742371569654</v>
+        <v>398.6262282462433</v>
       </c>
       <c r="L2" t="n">
-        <v>-492.5004462791052</v>
+        <v>531.1277161319805</v>
+      </c>
+      <c r="M2" t="n">
+        <v>450.2777030859564</v>
+      </c>
+      <c r="N2" t="n">
+        <v>183.1711209806231</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.201723443584241e-14</v>
+        <v>-7.560947585936579e-15</v>
       </c>
       <c r="B3" t="n">
-        <v>-62.08457910089774</v>
+        <v>23.38403063681879</v>
       </c>
       <c r="C3" t="n">
-        <v>-23.48720362495549</v>
+        <v>3.087311551431724</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.36766591826008</v>
+        <v>-9.008590981049302</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2693156030309629</v>
+        <v>2.173937277946462</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.289734910607411</v>
       </c>
       <c r="G3" t="n">
-        <v>-186.6041345315526</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-195.8058489108338</v>
+        <v>291.3037694099261</v>
       </c>
       <c r="I3" t="n">
-        <v>-379.1197653694511</v>
+        <v>297.6127288580574</v>
       </c>
       <c r="J3" t="n">
-        <v>-276.3008052942993</v>
+        <v>521.4227464777634</v>
       </c>
       <c r="K3" t="n">
-        <v>-322.3515312294784</v>
+        <v>495.0724263863388</v>
       </c>
       <c r="L3" t="n">
-        <v>-308.3608103848833</v>
+        <v>532.8768586758354</v>
+      </c>
+      <c r="M3" t="n">
+        <v>411.0256330149022</v>
+      </c>
+      <c r="N3" t="n">
+        <v>189.0067535000892</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.457349728839013e-15</v>
+        <v>3.01721362703714e-15</v>
       </c>
       <c r="B4" t="n">
-        <v>72.75488570955555</v>
+        <v>25.25084163834519</v>
       </c>
       <c r="C4" t="n">
-        <v>34.23745756584223</v>
+        <v>1.618781304780765</v>
       </c>
       <c r="D4" t="n">
-        <v>4.617280560125621</v>
+        <v>10.86023721632368</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.007553968119399785</v>
+        <v>-0.902771282409803</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3.623873603629091</v>
       </c>
       <c r="G4" t="n">
-        <v>-472.6376975985629</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-332.3410167754608</v>
+        <v>254.6370241030348</v>
       </c>
       <c r="I4" t="n">
-        <v>-216.7363583584817</v>
+        <v>284.8557852927199</v>
       </c>
       <c r="J4" t="n">
-        <v>-286.6285717259553</v>
+        <v>324.0156653796807</v>
       </c>
       <c r="K4" t="n">
-        <v>-370.6971102675043</v>
+        <v>421.4847359655286</v>
       </c>
       <c r="L4" t="n">
-        <v>-403.2383101266166</v>
+        <v>387.726928158306</v>
+      </c>
+      <c r="M4" t="n">
+        <v>323.2693899617532</v>
+      </c>
+      <c r="N4" t="n">
+        <v>452.8731553074604</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.131642017706478e-16</v>
+        <v>2.574751877899903e-15</v>
       </c>
       <c r="B5" t="n">
-        <v>-72.57703256250767</v>
+        <v>-25.26362869846291</v>
       </c>
       <c r="C5" t="n">
-        <v>-34.15898977735446</v>
+        <v>1.234187488208924</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.550929549321958</v>
+        <v>-11.87262017026268</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1365951122419682</v>
+        <v>-0.6197872071765848</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5.007273845178988</v>
       </c>
       <c r="G5" t="n">
-        <v>-429.9379982708162</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-486.2816184536979</v>
+        <v>331.9515871150373</v>
       </c>
       <c r="I5" t="n">
-        <v>-186.9257613804342</v>
+        <v>272.774484179764</v>
       </c>
       <c r="J5" t="n">
-        <v>-413.6107369559951</v>
+        <v>535.6952702337786</v>
       </c>
       <c r="K5" t="n">
-        <v>-464.1608131858724</v>
+        <v>486.7351854233103</v>
       </c>
       <c r="L5" t="n">
-        <v>-308.4628068165857</v>
+        <v>366.6186717879503</v>
+      </c>
+      <c r="M5" t="n">
+        <v>223.5342485504215</v>
+      </c>
+      <c r="N5" t="n">
+        <v>476.3452415249737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-2.586856717787989e-16</v>
+        <v>-7.017165746885825e-17</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.5983940329453121</v>
+        <v>10.58270616534834</v>
       </c>
       <c r="C6" t="n">
-        <v>34.27487797097394</v>
+        <v>14.63442026757189</v>
       </c>
       <c r="D6" t="n">
-        <v>4.627055717275937</v>
+        <v>-0.2287872707469437</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1993669690983227</v>
+        <v>-0.001416380688823152</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-5.618691890892688</v>
       </c>
       <c r="G6" t="n">
-        <v>-277.5879127195409</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-317.091171969849</v>
+        <v>299.8650832497679</v>
       </c>
       <c r="I6" t="n">
-        <v>-386.2729667306222</v>
+        <v>333.7551743371068</v>
       </c>
       <c r="J6" t="n">
-        <v>-332.9102484155094</v>
+        <v>446.5214854049892</v>
       </c>
       <c r="K6" t="n">
-        <v>-245.6896068973816</v>
+        <v>427.9430801760904</v>
       </c>
       <c r="L6" t="n">
-        <v>-199.6462680349517</v>
+        <v>384.0391582118506</v>
+      </c>
+      <c r="M6" t="n">
+        <v>420.5637087668171</v>
+      </c>
+      <c r="N6" t="n">
+        <v>305.8336987303861</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.234894165599741e-16</v>
+        <v>-1.317035652050331e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>-61.6228854673481</v>
+        <v>-13.02967321738174</v>
       </c>
       <c r="C7" t="n">
-        <v>-34.28187711272829</v>
+        <v>-14.64280858364535</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.632296312104169</v>
+        <v>-0.4001606693181877</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01594674427689886</v>
+        <v>0.613982466582634</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-3.972590086232081</v>
       </c>
       <c r="G7" t="n">
-        <v>-459.1254092749147</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-220.8499334632698</v>
+        <v>476.8376285164791</v>
       </c>
       <c r="I7" t="n">
-        <v>-476.4915834131096</v>
+        <v>490.82067122955</v>
       </c>
       <c r="J7" t="n">
-        <v>-486.1209820702944</v>
+        <v>292.737392862889</v>
       </c>
       <c r="K7" t="n">
-        <v>-356.5865921431373</v>
+        <v>185.511633953809</v>
       </c>
       <c r="L7" t="n">
-        <v>-297.8344952251817</v>
+        <v>258.0904042232194</v>
+      </c>
+      <c r="M7" t="n">
+        <v>512.3202300674109</v>
+      </c>
+      <c r="N7" t="n">
+        <v>408.9460414632738</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6.516266488591893e-16</v>
+        <v>-3.496257901222564e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>-21.9945015396075</v>
+        <v>-9.336086052653007</v>
       </c>
       <c r="C8" t="n">
-        <v>14.70241039399864</v>
+        <v>-0.5787390040059063</v>
       </c>
       <c r="D8" t="n">
-        <v>4.633380754714922</v>
+        <v>13.64704762127315</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.024105811999669</v>
+        <v>0.2303710582208956</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-5.476057275792131</v>
       </c>
       <c r="G8" t="n">
-        <v>-282.7392712665126</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-244.4867908893632</v>
+        <v>377.6560843318835</v>
       </c>
       <c r="I8" t="n">
-        <v>-286.0860656076363</v>
+        <v>248.6683378956409</v>
       </c>
       <c r="J8" t="n">
-        <v>-477.3969742148799</v>
+        <v>267.4680144484938</v>
       </c>
       <c r="K8" t="n">
-        <v>-440.6455081329881</v>
+        <v>437.1668650824727</v>
       </c>
       <c r="L8" t="n">
-        <v>-404.0443097978236</v>
+        <v>345.27647415659</v>
+      </c>
+      <c r="M8" t="n">
+        <v>193.024410252534</v>
+      </c>
+      <c r="N8" t="n">
+        <v>320.8433142422578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-2.273091110257183e-16</v>
+        <v>1.445407583328878e-16</v>
       </c>
       <c r="B9" t="n">
-        <v>61.56050512277194</v>
+        <v>-3.985431562076922</v>
       </c>
       <c r="C9" t="n">
-        <v>24.1379722413469</v>
+        <v>0.4265741715352532</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.633211881034514</v>
+        <v>-13.65032824037603</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03280685946515912</v>
+        <v>-0.1277426831440162</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-3.32529700402907</v>
       </c>
       <c r="G9" t="n">
-        <v>-483.2724634039739</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-196.5170722533677</v>
+        <v>249.9985615464464</v>
       </c>
       <c r="I9" t="n">
-        <v>-269.3900503189717</v>
+        <v>370.7390680836301</v>
       </c>
       <c r="J9" t="n">
-        <v>-436.739156961807</v>
+        <v>477.4571424066878</v>
       </c>
       <c r="K9" t="n">
-        <v>-471.6976033358526</v>
+        <v>239.378623245696</v>
       </c>
       <c r="L9" t="n">
-        <v>-320.5849019083331</v>
+        <v>216.7672603127323</v>
+      </c>
+      <c r="M9" t="n">
+        <v>459.8264558208631</v>
+      </c>
+      <c r="N9" t="n">
+        <v>445.0626888046711</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-2.287502100180515e-16</v>
+        <v>2.332201616289696e-16</v>
       </c>
       <c r="B10" t="n">
-        <v>21.64807069891622</v>
+        <v>3.808774281553613</v>
       </c>
       <c r="C10" t="n">
-        <v>24.6199410785954</v>
+        <v>-1.507017039162052</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.617437489580903</v>
+        <v>-7.936830801261921</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3845187133700474</v>
+        <v>5.647427834700743</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.05985764924645164</v>
       </c>
       <c r="G10" t="n">
-        <v>-441.4496276851401</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-510.5948830167984</v>
+        <v>417.3350706540347</v>
       </c>
       <c r="I10" t="n">
-        <v>-495.9386559183077</v>
+        <v>196.9513486628672</v>
       </c>
       <c r="J10" t="n">
-        <v>-193.0822109907045</v>
+        <v>300.8694369427828</v>
       </c>
       <c r="K10" t="n">
-        <v>-317.7947808786281</v>
+        <v>404.1290325466281</v>
       </c>
       <c r="L10" t="n">
-        <v>-258.7246384229464</v>
+        <v>520.233006026152</v>
+      </c>
+      <c r="M10" t="n">
+        <v>462.1768721192748</v>
+      </c>
+      <c r="N10" t="n">
+        <v>215.9306688942214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-3.161693472825149e-17</v>
+        <v>1.09895960883844e-16</v>
       </c>
       <c r="B11" t="n">
-        <v>-20.46079347430157</v>
+        <v>5.421000831259841</v>
       </c>
       <c r="C11" t="n">
-        <v>16.59279036407499</v>
+        <v>5.627686261272528</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.617363830806576</v>
+        <v>-4.832286318054987</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3845346664407691</v>
+        <v>-5.633515071190155</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0.1746654834004763</v>
       </c>
       <c r="G11" t="n">
-        <v>-372.1531707410059</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-244.7141334004037</v>
+        <v>263.0817695075536</v>
       </c>
       <c r="I11" t="n">
-        <v>-331.1444019380936</v>
+        <v>479.7050954374721</v>
       </c>
       <c r="J11" t="n">
-        <v>-519.2045320418721</v>
+        <v>462.0192327401265</v>
       </c>
       <c r="K11" t="n">
-        <v>-178.2864822662269</v>
+        <v>305.6256435626039</v>
       </c>
       <c r="L11" t="n">
-        <v>-434.1738024232443</v>
+        <v>234.1370418109174</v>
+      </c>
+      <c r="M11" t="n">
+        <v>314.9049457072525</v>
+      </c>
+      <c r="N11" t="n">
+        <v>183.382619330872</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-4.036147258561703e-16</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0.6988503604923154</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.2137667082140493</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>10.19780505181948</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.04553500618185997</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5.648279221083707</v>
       </c>
       <c r="G12" t="n">
-        <v>-214.4828959350884</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-423.4693951614913</v>
+        <v>428.8917608888394</v>
       </c>
       <c r="I12" t="n">
-        <v>-494.3416955883869</v>
+        <v>528.6693508946598</v>
       </c>
       <c r="J12" t="n">
-        <v>-431.8516367298919</v>
+        <v>502.7993131944282</v>
       </c>
       <c r="K12" t="n">
-        <v>-342.8861601677124</v>
+        <v>433.9815993523167</v>
       </c>
       <c r="L12" t="n">
-        <v>-226.7334697377379</v>
+        <v>275.2446062609552</v>
+      </c>
+      <c r="M12" t="n">
+        <v>422.0900361010226</v>
+      </c>
+      <c r="N12" t="n">
+        <v>486.9340782764598</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>8.665380563641304e-17</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>5.041427630829921</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.055096747866907</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-2.556767907115044</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.01999818532878022</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-5.647667547279767</v>
       </c>
       <c r="G13" t="n">
-        <v>-214.4828959350884</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-423.4693951614913</v>
+        <v>527.4936509956985</v>
       </c>
       <c r="I13" t="n">
-        <v>-494.3416955883869</v>
+        <v>204.3895625117081</v>
       </c>
       <c r="J13" t="n">
-        <v>-431.8516367298919</v>
+        <v>411.3284742979341</v>
       </c>
       <c r="K13" t="n">
-        <v>-342.8861601677124</v>
+        <v>435.6127895035814</v>
       </c>
       <c r="L13" t="n">
-        <v>-226.7334697377379</v>
+        <v>271.0384060829838</v>
+      </c>
+      <c r="M13" t="n">
+        <v>363.7931022109953</v>
+      </c>
+      <c r="N13" t="n">
+        <v>391.1755395445362</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Torque 1 max</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Torque 2 max</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Torque 3 max</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Torque 4 max</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Torque 5 max</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Torque 6 max</t>
-        </is>
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>437.1810426681801</v>
+      </c>
+      <c r="I14" t="n">
+        <v>367.1334171692797</v>
+      </c>
+      <c r="J14" t="n">
+        <v>498.5173187669812</v>
+      </c>
+      <c r="K14" t="n">
+        <v>217.0337851718957</v>
+      </c>
+      <c r="L14" t="n">
+        <v>181.6010117857254</v>
+      </c>
+      <c r="M14" t="n">
+        <v>397.1794861206096</v>
+      </c>
+      <c r="N14" t="n">
+        <v>459.9243322647536</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.158017126043946e-14</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>72.75488570955555</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34.27487797097394</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4.633380754714922</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3845187133700474</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>437.1810426681801</v>
+      </c>
+      <c r="I15" t="n">
+        <v>367.1334171692797</v>
+      </c>
+      <c r="J15" t="n">
+        <v>498.5173187669812</v>
+      </c>
+      <c r="K15" t="n">
+        <v>217.0337851718957</v>
+      </c>
+      <c r="L15" t="n">
+        <v>181.6010117857254</v>
+      </c>
+      <c r="M15" t="n">
+        <v>397.1794861206096</v>
+      </c>
+      <c r="N15" t="n">
+        <v>459.9243322647536</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Torque 1 max</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Torque 2 max</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Torque 3 max</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Torque 4 max</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Torque 5 max</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Torque 6 max</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Torque 7 max</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7.135609487268385e-15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>25.25084163834519</v>
+      </c>
+      <c r="C17" t="n">
+        <v>14.63442026757189</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13.64704762127315</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5.647427834700743</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.648279221083707</v>
+      </c>
+      <c r="G17" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_static_torque_calc.xlsx
@@ -490,530 +490,530 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7.135609487268385e-15</v>
+        <v>2.091084402029074e-15</v>
       </c>
       <c r="B2" t="n">
-        <v>22.25049312448555</v>
+        <v>-8.458597306597355</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.867269527210841</v>
+        <v>1.111588751874487</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.121035634862352</v>
+        <v>2.135759912283032</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.942561558001296</v>
+        <v>0.06531937323889681</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.521310373174949</v>
+        <v>0.01442690564597352</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>209.7898304122282</v>
+        <v>199.581576592411</v>
       </c>
       <c r="I2" t="n">
-        <v>517.5408897157441</v>
+        <v>305.8726010639211</v>
       </c>
       <c r="J2" t="n">
-        <v>516.7933625052171</v>
+        <v>246.8483767385426</v>
       </c>
       <c r="K2" t="n">
-        <v>398.6262282462433</v>
+        <v>459.6860818437322</v>
       </c>
       <c r="L2" t="n">
-        <v>531.1277161319805</v>
+        <v>339.459527560676</v>
       </c>
       <c r="M2" t="n">
-        <v>450.2777030859564</v>
+        <v>528.7828689279427</v>
       </c>
       <c r="N2" t="n">
-        <v>183.1711209806231</v>
+        <v>440.2046731874333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-7.560947585936579e-15</v>
+        <v>-2.095903073240358e-15</v>
       </c>
       <c r="B3" t="n">
-        <v>23.38403063681879</v>
+        <v>-8.391566670606764</v>
       </c>
       <c r="C3" t="n">
-        <v>3.087311551431724</v>
+        <v>-1.335612090260697</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.008590981049302</v>
+        <v>-2.240801731486746</v>
       </c>
       <c r="E3" t="n">
-        <v>2.173937277946462</v>
+        <v>-0.08255286808391003</v>
       </c>
       <c r="F3" t="n">
-        <v>0.289734910607411</v>
+        <v>-0.1333563633602791</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>291.3037694099261</v>
+        <v>485.3939670178032</v>
       </c>
       <c r="I3" t="n">
-        <v>297.6127288580574</v>
+        <v>436.6958470382312</v>
       </c>
       <c r="J3" t="n">
-        <v>521.4227464777634</v>
+        <v>299.169138471205</v>
       </c>
       <c r="K3" t="n">
-        <v>495.0724263863388</v>
+        <v>408.8494819426579</v>
       </c>
       <c r="L3" t="n">
-        <v>532.8768586758354</v>
+        <v>499.593551482129</v>
       </c>
       <c r="M3" t="n">
-        <v>411.0256330149022</v>
+        <v>515.803599794863</v>
       </c>
       <c r="N3" t="n">
-        <v>189.0067535000892</v>
+        <v>513.4625058407839</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3.01721362703714e-15</v>
+        <v>4.98041425468602e-17</v>
       </c>
       <c r="B4" t="n">
-        <v>25.25084163834519</v>
+        <v>8.763521341279153</v>
       </c>
       <c r="C4" t="n">
-        <v>1.618781304780765</v>
+        <v>0.01486666758628166</v>
       </c>
       <c r="D4" t="n">
-        <v>10.86023721632368</v>
+        <v>2.756253762499101</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.902771282409803</v>
+        <v>0.02911270517105026</v>
       </c>
       <c r="F4" t="n">
-        <v>3.623873603629091</v>
+        <v>0.1036626321243199</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>254.6370241030348</v>
+        <v>361.328496431315</v>
       </c>
       <c r="I4" t="n">
-        <v>284.8557852927199</v>
+        <v>268.1518919403587</v>
       </c>
       <c r="J4" t="n">
-        <v>324.0156653796807</v>
+        <v>359.6034521980309</v>
       </c>
       <c r="K4" t="n">
-        <v>421.4847359655286</v>
+        <v>200.0524871720202</v>
       </c>
       <c r="L4" t="n">
-        <v>387.726928158306</v>
+        <v>320.3586055206772</v>
       </c>
       <c r="M4" t="n">
-        <v>323.2693899617532</v>
+        <v>238.119000005915</v>
       </c>
       <c r="N4" t="n">
-        <v>452.8731553074604</v>
+        <v>271.1118778072905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.574751877899903e-15</v>
+        <v>4.888413102879092e-16</v>
       </c>
       <c r="B5" t="n">
-        <v>-25.26362869846291</v>
+        <v>-8.759754475949025</v>
       </c>
       <c r="C5" t="n">
-        <v>1.234187488208924</v>
+        <v>0.270071394342298</v>
       </c>
       <c r="D5" t="n">
-        <v>-11.87262017026268</v>
+        <v>-1.374631517555107</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6197872071765848</v>
+        <v>-0.0665519957554345</v>
       </c>
       <c r="F5" t="n">
-        <v>5.007273845178988</v>
+        <v>-0.1425444911655587</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>331.9515871150373</v>
+        <v>477.528222691642</v>
       </c>
       <c r="I5" t="n">
-        <v>272.774484179764</v>
+        <v>502.3270818423769</v>
       </c>
       <c r="J5" t="n">
-        <v>535.6952702337786</v>
+        <v>197.6445055132067</v>
       </c>
       <c r="K5" t="n">
-        <v>486.7351854233103</v>
+        <v>214.344379074006</v>
       </c>
       <c r="L5" t="n">
-        <v>366.6186717879503</v>
+        <v>316.9809979180069</v>
       </c>
       <c r="M5" t="n">
-        <v>223.5342485504215</v>
+        <v>479.4858432737691</v>
       </c>
       <c r="N5" t="n">
-        <v>476.3452415249737</v>
+        <v>389.1309435996199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-7.017165746885825e-17</v>
+        <v>-9.286157221446446e-17</v>
       </c>
       <c r="B6" t="n">
-        <v>10.58270616534834</v>
+        <v>5.735982617684324</v>
       </c>
       <c r="C6" t="n">
-        <v>14.63442026757189</v>
+        <v>3.442763122806434</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2287872707469437</v>
+        <v>-0.446002018757696</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001416380688823152</v>
+        <v>-0.08222631999044433</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.618691890892688</v>
+        <v>-0.1340991022356879</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>299.8650832497679</v>
+        <v>509.7478739052677</v>
       </c>
       <c r="I6" t="n">
-        <v>333.7551743371068</v>
+        <v>440.5642646229581</v>
       </c>
       <c r="J6" t="n">
-        <v>446.5214854049892</v>
+        <v>301.5895372471006</v>
       </c>
       <c r="K6" t="n">
-        <v>427.9430801760904</v>
+        <v>348.910821684365</v>
       </c>
       <c r="L6" t="n">
-        <v>384.0391582118506</v>
+        <v>514.9436092261838</v>
       </c>
       <c r="M6" t="n">
-        <v>420.5637087668171</v>
+        <v>512.9683443023638</v>
       </c>
       <c r="N6" t="n">
-        <v>305.8336987303861</v>
+        <v>459.0127361325627</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.317035652050331e-16</v>
+        <v>-2.126346206755841e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>-13.02967321738174</v>
+        <v>-6.192284577616161</v>
       </c>
       <c r="C7" t="n">
-        <v>-14.64280858364535</v>
+        <v>-3.443418641811209</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4001606693181877</v>
+        <v>0.2657907344864118</v>
       </c>
       <c r="E7" t="n">
-        <v>0.613982466582634</v>
+        <v>-0.01329079215864823</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.972590086232081</v>
+        <v>-0.08231174106343116</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>476.8376285164791</v>
+        <v>395.3277419870796</v>
       </c>
       <c r="I7" t="n">
-        <v>490.82067122955</v>
+        <v>241.8307080666694</v>
       </c>
       <c r="J7" t="n">
-        <v>292.737392862889</v>
+        <v>372.6260536919472</v>
       </c>
       <c r="K7" t="n">
-        <v>185.511633953809</v>
+        <v>475.0405701949384</v>
       </c>
       <c r="L7" t="n">
-        <v>258.0904042232194</v>
+        <v>392.6463691999913</v>
       </c>
       <c r="M7" t="n">
-        <v>512.3202300674109</v>
+        <v>363.6316180194382</v>
       </c>
       <c r="N7" t="n">
-        <v>408.9460414632738</v>
+        <v>476.4951506109616</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-3.496257901222564e-16</v>
+        <v>-3.979881964768324e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>-9.336086052653007</v>
+        <v>6.192282068997668</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5787390040059063</v>
+        <v>0.1514202957827768</v>
       </c>
       <c r="D8" t="n">
-        <v>13.64704762127315</v>
+        <v>2.865031990409634</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2303710582208956</v>
+        <v>0.01667243577036912</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.476057275792131</v>
+        <v>0.1201450936561008</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>377.6560843318835</v>
+        <v>382.1446781070459</v>
       </c>
       <c r="I8" t="n">
-        <v>248.6683378956409</v>
+        <v>192.1938263547758</v>
       </c>
       <c r="J8" t="n">
-        <v>267.4680144484938</v>
+        <v>407.0807806342549</v>
       </c>
       <c r="K8" t="n">
-        <v>437.1668650824727</v>
+        <v>289.2335407138834</v>
       </c>
       <c r="L8" t="n">
-        <v>345.27647415659</v>
+        <v>377.4210011138813</v>
       </c>
       <c r="M8" t="n">
-        <v>193.024410252534</v>
+        <v>221.5690860109626</v>
       </c>
       <c r="N8" t="n">
-        <v>320.8433142422578</v>
+        <v>303.5333163508629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.445407583328878e-16</v>
+        <v>8.641617607940851e-17</v>
       </c>
       <c r="B9" t="n">
-        <v>-3.985431562076922</v>
+        <v>3.67769799936344</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4265741715352532</v>
+        <v>0.04966293174512561</v>
       </c>
       <c r="D9" t="n">
-        <v>-13.65032824037603</v>
+        <v>-2.869848252803546</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1277426831440162</v>
+        <v>-0.0401212008750032</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.32529700402907</v>
+        <v>-0.09090384949421347</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>249.9985615464464</v>
+        <v>395.920800398075</v>
       </c>
       <c r="I9" t="n">
-        <v>370.7390680836301</v>
+        <v>312.5026810671708</v>
       </c>
       <c r="J9" t="n">
-        <v>477.4571424066878</v>
+        <v>329.3006601180693</v>
       </c>
       <c r="K9" t="n">
-        <v>239.378623245696</v>
+        <v>448.8695762947438</v>
       </c>
       <c r="L9" t="n">
-        <v>216.7672603127323</v>
+        <v>491.5325476948781</v>
       </c>
       <c r="M9" t="n">
-        <v>459.8264558208631</v>
+        <v>372.3057860108257</v>
       </c>
       <c r="N9" t="n">
-        <v>445.0626888046711</v>
+        <v>410.6200076527715</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.332201616289696e-16</v>
+        <v>-9.308170892949728e-17</v>
       </c>
       <c r="B10" t="n">
-        <v>3.808774281553613</v>
+        <v>6.638953409829795</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.507017039162052</v>
+        <v>0.7737428675330913</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.936830801261921</v>
+        <v>-2.332293560020399</v>
       </c>
       <c r="E10" t="n">
-        <v>5.647427834700743</v>
+        <v>0.1711908461494442</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.05985764924645164</v>
+        <v>0.004158360967413591</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>417.3350706540347</v>
+        <v>354.5112715827544</v>
       </c>
       <c r="I10" t="n">
-        <v>196.9513486628672</v>
+        <v>232.0579089482918</v>
       </c>
       <c r="J10" t="n">
-        <v>300.8694369427828</v>
+        <v>346.1937065514103</v>
       </c>
       <c r="K10" t="n">
-        <v>404.1290325466281</v>
+        <v>309.4438411410486</v>
       </c>
       <c r="L10" t="n">
-        <v>520.233006026152</v>
+        <v>401.3968895387717</v>
       </c>
       <c r="M10" t="n">
-        <v>462.1768721192748</v>
+        <v>484.9806782256219</v>
       </c>
       <c r="N10" t="n">
-        <v>215.9306688942214</v>
+        <v>293.3333574111562</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.09895960883844e-16</v>
+        <v>-7.293847233907031e-16</v>
       </c>
       <c r="B11" t="n">
-        <v>5.421000831259841</v>
+        <v>8.59929693333806</v>
       </c>
       <c r="C11" t="n">
-        <v>5.627686261272528</v>
+        <v>0.5068120455590905</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.832286318054987</v>
+        <v>1.086057945093318</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.633515071190155</v>
+        <v>-0.1709812011493719</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1746654834004763</v>
+        <v>0.005173503234148789</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>263.0817695075536</v>
+        <v>537.3101253217721</v>
       </c>
       <c r="I11" t="n">
-        <v>479.7050954374721</v>
+        <v>242.9785987216519</v>
       </c>
       <c r="J11" t="n">
-        <v>462.0192327401265</v>
+        <v>333.2409847018682</v>
       </c>
       <c r="K11" t="n">
-        <v>305.6256435626039</v>
+        <v>513.3010088635672</v>
       </c>
       <c r="L11" t="n">
-        <v>234.1370418109174</v>
+        <v>516.5222581864437</v>
       </c>
       <c r="M11" t="n">
-        <v>314.9049457072525</v>
+        <v>201.7686216182516</v>
       </c>
       <c r="N11" t="n">
-        <v>183.382619330872</v>
+        <v>192.2909810459731</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-4.036147258561703e-16</v>
+        <v>3.268428559121734e-17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.6988503604923154</v>
+        <v>2.34690668613656</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2137667082140493</v>
+        <v>0.1892166042793877</v>
       </c>
       <c r="D12" t="n">
-        <v>10.19780505181948</v>
+        <v>-0.4576230225017918</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04553500618185997</v>
+        <v>0.007830261864119746</v>
       </c>
       <c r="F12" t="n">
-        <v>5.648279221083707</v>
+        <v>0.1548768194610479</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>428.8917608888394</v>
+        <v>243.412783090511</v>
       </c>
       <c r="I12" t="n">
-        <v>528.6693508946598</v>
+        <v>490.6140698146687</v>
       </c>
       <c r="J12" t="n">
-        <v>502.7993131944282</v>
+        <v>398.8873602718414</v>
       </c>
       <c r="K12" t="n">
-        <v>433.9815993523167</v>
+        <v>442.0081865252918</v>
       </c>
       <c r="L12" t="n">
-        <v>275.2446062609552</v>
+        <v>521.1176628360802</v>
       </c>
       <c r="M12" t="n">
-        <v>422.0900361010226</v>
+        <v>230.1440907067151</v>
       </c>
       <c r="N12" t="n">
-        <v>486.9340782764598</v>
+        <v>230.1042292712779</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8.665380563641304e-17</v>
+        <v>-4.881716712170072e-18</v>
       </c>
       <c r="B13" t="n">
-        <v>5.041427630829921</v>
+        <v>0.6922730380336786</v>
       </c>
       <c r="C13" t="n">
-        <v>1.055096747866907</v>
+        <v>-0.000642904925759387</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.556767907115044</v>
+        <v>-0.4929182635350759</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01999818532878022</v>
+        <v>0.007685180859486992</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.647667547279767</v>
+        <v>-0.1548969613412612</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>527.4936509956985</v>
+        <v>395.671394524408</v>
       </c>
       <c r="I13" t="n">
-        <v>204.3895625117081</v>
+        <v>270.2762959640062</v>
       </c>
       <c r="J13" t="n">
-        <v>411.3284742979341</v>
+        <v>195.7589088812408</v>
       </c>
       <c r="K13" t="n">
-        <v>435.6127895035814</v>
+        <v>350.1185314530817</v>
       </c>
       <c r="L13" t="n">
-        <v>271.0384060829838</v>
+        <v>331.151126844255</v>
       </c>
       <c r="M13" t="n">
-        <v>363.7931022109953</v>
+        <v>311.9634251843502</v>
       </c>
       <c r="N13" t="n">
-        <v>391.1755395445362</v>
+        <v>400.647436074185</v>
       </c>
     </row>
     <row r="14">
@@ -1039,25 +1039,25 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>437.1810426681801</v>
+        <v>190.6817059191295</v>
       </c>
       <c r="I14" t="n">
-        <v>367.1334171692797</v>
+        <v>407.1578754882274</v>
       </c>
       <c r="J14" t="n">
-        <v>498.5173187669812</v>
+        <v>229.9306121754371</v>
       </c>
       <c r="K14" t="n">
-        <v>217.0337851718957</v>
+        <v>515.3986112461459</v>
       </c>
       <c r="L14" t="n">
-        <v>181.6010117857254</v>
+        <v>343.3926429191748</v>
       </c>
       <c r="M14" t="n">
-        <v>397.1794861206096</v>
+        <v>519.2475319439154</v>
       </c>
       <c r="N14" t="n">
-        <v>459.9243322647536</v>
+        <v>182.5216974445223</v>
       </c>
     </row>
     <row r="15">
@@ -1083,25 +1083,25 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>437.1810426681801</v>
+        <v>190.6817059191295</v>
       </c>
       <c r="I15" t="n">
-        <v>367.1334171692797</v>
+        <v>407.1578754882274</v>
       </c>
       <c r="J15" t="n">
-        <v>498.5173187669812</v>
+        <v>229.9306121754371</v>
       </c>
       <c r="K15" t="n">
-        <v>217.0337851718957</v>
+        <v>515.3986112461459</v>
       </c>
       <c r="L15" t="n">
-        <v>181.6010117857254</v>
+        <v>343.3926429191748</v>
       </c>
       <c r="M15" t="n">
-        <v>397.1794861206096</v>
+        <v>519.2475319439154</v>
       </c>
       <c r="N15" t="n">
-        <v>459.9243322647536</v>
+        <v>182.5216974445223</v>
       </c>
     </row>
     <row r="16">
@@ -1143,22 +1143,22 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7.135609487268385e-15</v>
+        <v>2.091084402029074e-15</v>
       </c>
       <c r="B17" t="n">
-        <v>25.25084163834519</v>
+        <v>8.763521341279153</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63442026757189</v>
+        <v>3.442763122806434</v>
       </c>
       <c r="D17" t="n">
-        <v>13.64704762127315</v>
+        <v>2.865031990409634</v>
       </c>
       <c r="E17" t="n">
-        <v>5.647427834700743</v>
+        <v>0.1711908461494442</v>
       </c>
       <c r="F17" t="n">
-        <v>5.648279221083707</v>
+        <v>0.1548768194610479</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
